--- a/Data-file.xlsx
+++ b/Data-file.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="512" documentId="8_{3CAE69A3-AE5B-4257-93BE-F3BFAEF5261B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CACEB46B-7809-477E-A0D5-DE28D8BF9865}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="7" xr2:uid="{8A8E2015-1165-48D9-8246-BE8999149D44}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{8A8E2015-1165-48D9-8246-BE8999149D44}"/>
   </bookViews>
   <sheets>
     <sheet name="ACC 3" sheetId="1" r:id="rId1"/>
@@ -741,7 +741,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2018,14 +2018,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{862506E9-25B6-4CBA-A38B-FADA62B5D706}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:4" ht="13.9" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2039,7 +2039,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:4" ht="16.149999999999999" thickBot="1">
       <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:4" ht="16.149999999999999" thickBot="1">
       <c r="A3" s="14" t="s">
         <v>5</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" ht="15.75">
       <c r="A4" s="16" t="s">
         <v>6</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" ht="15.75">
       <c r="A5" s="30" t="s">
         <v>7</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>1815</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" ht="15.75">
       <c r="A6" s="30" t="s">
         <v>8</v>
       </c>
@@ -2110,7 +2110,7 @@
         <v>2688</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" ht="15.75">
       <c r="A7" s="30" t="s">
         <v>9</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>3493</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" ht="15.75">
       <c r="A8" s="30" t="s">
         <v>10</v>
       </c>
@@ -2140,7 +2140,7 @@
         <v>4615</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" ht="15.75">
       <c r="A9" s="30" t="s">
         <v>218</v>
       </c>
@@ -2163,13 +2163,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9917535D-21FB-4B58-A8DD-F27CB281E1B3}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="23.73046875" customWidth="1"/>
+    <col min="1" max="1" width="23.75" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" ht="13.9" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -2177,7 +2177,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" ht="15.4" thickBot="1">
       <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
@@ -2185,7 +2185,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" ht="15.4" thickBot="1">
       <c r="A3" s="5" t="s">
         <v>15</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" ht="15.4" thickBot="1">
       <c r="A4" s="7" t="s">
         <v>17</v>
       </c>
@@ -2201,7 +2201,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30.4" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" ht="30.4" thickBot="1">
       <c r="A5" s="5" t="s">
         <v>19</v>
       </c>
@@ -2209,7 +2209,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" ht="15.4" thickBot="1">
       <c r="A6" s="7" t="s">
         <v>20</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="30.4" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" ht="30.4" thickBot="1">
       <c r="A7" s="5" t="s">
         <v>21</v>
       </c>
@@ -2225,7 +2225,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" ht="15.4" thickBot="1">
       <c r="A8" s="7" t="s">
         <v>22</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:2" ht="15.4" thickBot="1">
       <c r="A9" s="5" t="s">
         <v>23</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:2" ht="15.4" thickBot="1">
       <c r="A10" s="7" t="s">
         <v>25</v>
       </c>
@@ -2257,14 +2257,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F89D7ACF-216A-4C43-82E3-F1E9ECF11B39}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="24.59765625" customWidth="1"/>
+    <col min="1" max="1" width="24.625" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="41.1328125" customWidth="1"/>
+    <col min="3" max="3" width="41.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="31.9" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3" ht="31.9" thickBot="1">
       <c r="A1" s="19" t="s">
         <v>27</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="47.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:3" ht="47.65" thickBot="1">
       <c r="A2" s="23" t="s">
         <v>30</v>
       </c>
@@ -2286,7 +2286,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="47.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:3" ht="47.65" thickBot="1">
       <c r="A3" s="23" t="s">
         <v>33</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="47.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:3" ht="47.65" thickBot="1">
       <c r="A4" s="23" t="s">
         <v>35</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="47.25" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" ht="47.25">
       <c r="A5" s="25" t="s">
         <v>37</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="47.25" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" ht="47.25">
       <c r="A6" s="28" t="s">
         <v>40</v>
       </c>
@@ -2330,7 +2330,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" ht="15.75">
       <c r="A7" s="28" t="s">
         <v>42</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" ht="15.75">
       <c r="A8" s="28" t="s">
         <v>45</v>
       </c>
@@ -2352,7 +2352,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" ht="15.75">
       <c r="A9" s="28" t="s">
         <v>48</v>
       </c>
@@ -2363,7 +2363,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:3" ht="15.75">
       <c r="A10" s="28" t="s">
         <v>50</v>
       </c>
@@ -2380,12 +2380,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73E19115-1CD0-4934-BDF4-4937A2D87F36}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="16.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>52</v>
       </c>
@@ -2396,7 +2396,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>55</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>224</v>
       </c>
@@ -2427,14 +2427,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73BDED7B-F217-445A-9C06-91034F503C5D}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="27.73046875" customWidth="1"/>
-    <col min="2" max="3" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.265625" customWidth="1"/>
+    <col min="1" max="1" width="27.75" customWidth="1"/>
+    <col min="2" max="3" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.15" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:4" ht="14.25" thickBot="1">
       <c r="A1" s="8" t="s">
         <v>56</v>
       </c>
@@ -2448,7 +2448,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" ht="13.9">
       <c r="A2" s="10" t="s">
         <v>60</v>
       </c>
@@ -2463,7 +2463,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" ht="13.9">
       <c r="A3" s="10" t="s">
         <v>61</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" ht="13.9">
       <c r="A4" s="10" t="s">
         <v>62</v>
       </c>
@@ -2493,7 +2493,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" ht="13.9">
       <c r="A5" s="10" t="s">
         <v>63</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" ht="13.9">
       <c r="A6" s="10" t="s">
         <v>64</v>
       </c>
@@ -2523,7 +2523,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" ht="13.9">
       <c r="A7" s="10" t="s">
         <v>65</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" ht="13.9">
       <c r="A8" s="10" t="s">
         <v>66</v>
       </c>
@@ -2553,7 +2553,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:4" ht="14.25" thickBot="1">
       <c r="A9" s="10" t="s">
         <v>67</v>
       </c>
@@ -2578,7 +2578,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{937E703F-939A-4FE6-A55F-3284F68BDE73}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2588,20 +2588,20 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC87E3DB-D54A-4C9B-8DF9-428C70D3A6F3}">
   <dimension ref="A1:W303"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.73046875" customWidth="1"/>
-    <col min="5" max="5" width="14.73046875" customWidth="1"/>
+    <col min="2" max="2" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.75" customWidth="1"/>
+    <col min="5" max="5" width="14.75" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="23" max="23" width="2.73046875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="2.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="39" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" s="39" customFormat="1" ht="42.75" customHeight="1">
       <c r="A1" s="37" t="s">
         <v>68</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" ht="15.75">
       <c r="A2" s="35" t="s">
         <v>80</v>
       </c>
@@ -2665,7 +2665,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" ht="15.75">
       <c r="A3" s="35" t="s">
         <v>87</v>
       </c>
@@ -2691,7 +2691,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" ht="15.75">
       <c r="A4" s="35" t="s">
         <v>87</v>
       </c>
@@ -2717,7 +2717,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" ht="15.75">
       <c r="A5" s="35" t="s">
         <v>98</v>
       </c>
@@ -2743,7 +2743,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" ht="15.75">
       <c r="A6" s="35" t="s">
         <v>105</v>
       </c>
@@ -2769,7 +2769,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" ht="15.75">
       <c r="A7" s="35" t="s">
         <v>91</v>
       </c>
@@ -2795,7 +2795,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" ht="15.75">
       <c r="A8" s="35" t="s">
         <v>90</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" ht="15.75">
       <c r="A9" s="35" t="s">
         <v>92</v>
       </c>
@@ -2847,7 +2847,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" ht="15.75">
       <c r="A10" s="35" t="s">
         <v>124</v>
       </c>
@@ -2873,7 +2873,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" ht="15.75">
       <c r="A11" s="35" t="s">
         <v>127</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12" ht="15.75">
       <c r="A12" s="35" t="s">
         <v>117</v>
       </c>
@@ -2925,7 +2925,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:12" ht="15.75">
       <c r="A13" s="35" t="s">
         <v>122</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" ht="15.75">
       <c r="A14" s="35" t="s">
         <v>85</v>
       </c>
@@ -2977,7 +2977,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12" ht="15.75">
       <c r="A15" s="35" t="s">
         <v>86</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" ht="15.75">
       <c r="A16" s="35" t="s">
         <v>84</v>
       </c>
@@ -3029,7 +3029,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:8" ht="15.75">
       <c r="A17" s="35" t="s">
         <v>123</v>
       </c>
@@ -3055,7 +3055,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:8" ht="15.75">
       <c r="A18" s="35" t="s">
         <v>149</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:8" ht="15.75">
       <c r="A19" s="35" t="s">
         <v>114</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:8" ht="15.75">
       <c r="A20" s="35" t="s">
         <v>154</v>
       </c>
@@ -3133,7 +3133,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:8" ht="15.75">
       <c r="A21" s="35" t="s">
         <v>113</v>
       </c>
@@ -3159,7 +3159,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:8" ht="15.75">
       <c r="A22" s="36"/>
       <c r="B22" s="36"/>
       <c r="C22" s="37" t="s">
@@ -3181,7 +3181,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.75" hidden="1" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:8" ht="15.75" hidden="1">
       <c r="A23" s="33"/>
       <c r="B23" s="33"/>
       <c r="C23" s="34" t="s">
@@ -3201,7 +3201,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="303" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="303" spans="23:23">
       <c r="W303" t="s">
         <v>170</v>
       </c>
@@ -3214,16 +3214,16 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{742D201E-24F7-4C61-8302-831552FAC820}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="13.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6">
       <c r="A1" s="43" t="s">
         <v>171</v>
       </c>
@@ -3243,7 +3243,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6">
       <c r="A2" s="44"/>
       <c r="B2" s="44"/>
       <c r="C2" s="44"/>
@@ -3251,7 +3251,7 @@
       <c r="E2" s="44"/>
       <c r="F2" s="44"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6">
       <c r="A3" s="44"/>
       <c r="B3" s="44"/>
       <c r="C3" s="44"/>
@@ -3259,7 +3259,7 @@
       <c r="E3" s="44"/>
       <c r="F3" s="44"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6">
       <c r="A4" s="32">
         <v>1</v>
       </c>
@@ -3279,7 +3279,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6">
       <c r="A5" s="32">
         <v>2</v>
       </c>
@@ -3299,7 +3299,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6">
       <c r="A6" s="32">
         <v>3</v>
       </c>
@@ -3319,7 +3319,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6">
       <c r="A7" s="32">
         <v>4</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6">
       <c r="A8" s="32">
         <v>5</v>
       </c>
@@ -3355,7 +3355,7 @@
       <c r="E8" s="32"/>
       <c r="F8" s="32"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6">
       <c r="A9" s="32"/>
       <c r="B9" s="40" t="s">
         <v>191</v>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="F9" s="32"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6">
       <c r="A10" s="32">
         <v>6</v>
       </c>
@@ -3383,7 +3383,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="32"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6">
       <c r="A11" s="32">
         <v>7</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6">
       <c r="A12" s="32">
         <v>8</v>
       </c>
@@ -3423,7 +3423,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6">
       <c r="A13" s="32">
         <v>9</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6">
       <c r="A14" s="32">
         <v>10</v>
       </c>
@@ -3459,7 +3459,7 @@
       <c r="E14" s="32"/>
       <c r="F14" s="32"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6">
       <c r="A15" s="32">
         <v>11</v>
       </c>
@@ -3479,7 +3479,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6">
       <c r="A16" s="32">
         <v>12</v>
       </c>
@@ -3495,7 +3495,7 @@
       <c r="E16" s="32"/>
       <c r="F16" s="32"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6">
       <c r="A17" s="32">
         <v>13</v>
       </c>
@@ -3511,7 +3511,7 @@
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6">
       <c r="B18" s="40" t="s">
         <v>216</v>
       </c>

--- a/Data-file.xlsx
+++ b/Data-file.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="512" documentId="8_{3CAE69A3-AE5B-4257-93BE-F3BFAEF5261B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CACEB46B-7809-477E-A0D5-DE28D8BF9865}"/>
+  <xr:revisionPtr revIDLastSave="513" documentId="8_{3CAE69A3-AE5B-4257-93BE-F3BFAEF5261B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F7096FD-64EE-4A16-9CA5-C7A15F64E88C}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{8A8E2015-1165-48D9-8246-BE8999149D44}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{8A8E2015-1165-48D9-8246-BE8999149D44}"/>
   </bookViews>
   <sheets>
     <sheet name="ACC 3" sheetId="1" r:id="rId1"/>
@@ -741,7 +741,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2018,14 +2018,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{862506E9-25B6-4CBA-A38B-FADA62B5D706}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="13.9" thickBot="1">
+    <row r="1" spans="1:4" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2039,7 +2039,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="16.149999999999999" thickBot="1">
+    <row r="2" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="16.149999999999999" thickBot="1">
+    <row r="3" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>5</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75">
+    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>6</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75">
+    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="30" t="s">
         <v>7</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>1815</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75">
+    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="30" t="s">
         <v>8</v>
       </c>
@@ -2110,7 +2110,7 @@
         <v>2688</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.75">
+    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="30" t="s">
         <v>9</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>3493</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75">
+    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="30" t="s">
         <v>10</v>
       </c>
@@ -2140,7 +2140,7 @@
         <v>4615</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.75">
+    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="30" t="s">
         <v>218</v>
       </c>
@@ -2148,11 +2148,11 @@
         <v>297</v>
       </c>
       <c r="C9" s="30">
-        <v>106</v>
+        <v>211</v>
       </c>
       <c r="D9" s="31">
         <f>D8+C9</f>
-        <v>4721</v>
+        <v>4826</v>
       </c>
     </row>
   </sheetData>
@@ -2163,13 +2163,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9917535D-21FB-4B58-A8DD-F27CB281E1B3}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.75" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.9" thickBot="1">
+    <row r="1" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -2177,7 +2177,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.4" thickBot="1">
+    <row r="2" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
@@ -2185,7 +2185,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.4" thickBot="1">
+    <row r="3" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>15</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.4" thickBot="1">
+    <row r="4" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>17</v>
       </c>
@@ -2201,7 +2201,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30.4" thickBot="1">
+    <row r="5" spans="1:2" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>19</v>
       </c>
@@ -2209,7 +2209,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.4" thickBot="1">
+    <row r="6" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>20</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="30.4" thickBot="1">
+    <row r="7" spans="1:2" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>21</v>
       </c>
@@ -2225,7 +2225,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.4" thickBot="1">
+    <row r="8" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>22</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.4" thickBot="1">
+    <row r="9" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>23</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.4" thickBot="1">
+    <row r="10" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>25</v>
       </c>
@@ -2257,14 +2257,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F89D7ACF-216A-4C43-82E3-F1E9ECF11B39}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.625" customWidth="1"/>
+    <col min="1" max="1" width="24.5703125" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="41.125" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="31.9" thickBot="1">
+    <row r="1" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>27</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="47.65" thickBot="1">
+    <row r="2" spans="1:3" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>30</v>
       </c>
@@ -2286,7 +2286,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="47.65" thickBot="1">
+    <row r="3" spans="1:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>33</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="47.65" thickBot="1">
+    <row r="4" spans="1:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="23" t="s">
         <v>35</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="47.25">
+    <row r="5" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
         <v>37</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="47.25">
+    <row r="6" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
         <v>40</v>
       </c>
@@ -2330,7 +2330,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
         <v>42</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75">
+    <row r="8" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
         <v>45</v>
       </c>
@@ -2352,7 +2352,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75">
+    <row r="9" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
         <v>48</v>
       </c>
@@ -2363,7 +2363,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
         <v>50</v>
       </c>
@@ -2380,12 +2380,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73E19115-1CD0-4934-BDF4-4937A2D87F36}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>52</v>
       </c>
@@ -2396,7 +2396,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>55</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>224</v>
       </c>
@@ -2427,14 +2427,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73BDED7B-F217-445A-9C06-91034F503C5D}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.75" customWidth="1"/>
-    <col min="2" max="3" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.25" customWidth="1"/>
+    <col min="1" max="1" width="27.7109375" customWidth="1"/>
+    <col min="2" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.25" thickBot="1">
+    <row r="1" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>56</v>
       </c>
@@ -2448,7 +2448,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="13.9">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>60</v>
       </c>
@@ -2463,7 +2463,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="13.9">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>61</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="13.9">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>62</v>
       </c>
@@ -2493,7 +2493,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="13.9">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>63</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="13.9">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>64</v>
       </c>
@@ -2523,7 +2523,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="13.9">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>65</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="13.9">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>66</v>
       </c>
@@ -2553,7 +2553,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="14.25" thickBot="1">
+    <row r="9" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>67</v>
       </c>
@@ -2578,7 +2578,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{937E703F-939A-4FE6-A55F-3284F68BDE73}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2588,20 +2588,20 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC87E3DB-D54A-4C9B-8DF9-428C70D3A6F3}">
   <dimension ref="A1:W303"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.75" customWidth="1"/>
-    <col min="5" max="5" width="14.75" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="23" max="23" width="2.75" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="2.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="39" customFormat="1" ht="42.75" customHeight="1">
+    <row r="1" spans="1:12" s="39" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="37" t="s">
         <v>68</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.75">
+    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
         <v>80</v>
       </c>
@@ -2665,7 +2665,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15.75">
+    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="35" t="s">
         <v>87</v>
       </c>
@@ -2691,7 +2691,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15.75">
+    <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>87</v>
       </c>
@@ -2717,7 +2717,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15.75">
+    <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>98</v>
       </c>
@@ -2743,7 +2743,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15.75">
+    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>105</v>
       </c>
@@ -2769,7 +2769,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15.75">
+    <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>91</v>
       </c>
@@ -2795,7 +2795,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15.75">
+    <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="35" t="s">
         <v>90</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15.75">
+    <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="35" t="s">
         <v>92</v>
       </c>
@@ -2847,7 +2847,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15.75">
+    <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="35" t="s">
         <v>124</v>
       </c>
@@ -2873,7 +2873,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15.75">
+    <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="35" t="s">
         <v>127</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15.75">
+    <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="35" t="s">
         <v>117</v>
       </c>
@@ -2925,7 +2925,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15.75">
+    <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="35" t="s">
         <v>122</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15.75">
+    <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="35" t="s">
         <v>85</v>
       </c>
@@ -2977,7 +2977,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15.75">
+    <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="35" t="s">
         <v>86</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15.75">
+    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="35" t="s">
         <v>84</v>
       </c>
@@ -3029,7 +3029,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.75">
+    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="35" t="s">
         <v>123</v>
       </c>
@@ -3055,7 +3055,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.75">
+    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="35" t="s">
         <v>149</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.75">
+    <row r="19" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A19" s="35" t="s">
         <v>114</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.75">
+    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="35" t="s">
         <v>154</v>
       </c>
@@ -3133,7 +3133,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.75">
+    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="35" t="s">
         <v>113</v>
       </c>
@@ -3159,7 +3159,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.75">
+    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="36"/>
       <c r="B22" s="36"/>
       <c r="C22" s="37" t="s">
@@ -3181,7 +3181,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.75" hidden="1">
+    <row r="23" spans="1:8" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="33"/>
       <c r="B23" s="33"/>
       <c r="C23" s="34" t="s">
@@ -3201,7 +3201,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="303" spans="23:23">
+    <row r="303" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W303" t="s">
         <v>170</v>
       </c>
@@ -3214,16 +3214,16 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{742D201E-24F7-4C61-8302-831552FAC820}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="43" t="s">
         <v>171</v>
       </c>
@@ -3243,7 +3243,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="44"/>
       <c r="B2" s="44"/>
       <c r="C2" s="44"/>
@@ -3251,7 +3251,7 @@
       <c r="E2" s="44"/>
       <c r="F2" s="44"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="44"/>
       <c r="B3" s="44"/>
       <c r="C3" s="44"/>
@@ -3259,7 +3259,7 @@
       <c r="E3" s="44"/>
       <c r="F3" s="44"/>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="32">
         <v>1</v>
       </c>
@@ -3279,7 +3279,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="32">
         <v>2</v>
       </c>
@@ -3299,7 +3299,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="32">
         <v>3</v>
       </c>
@@ -3319,7 +3319,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="32">
         <v>4</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="32">
         <v>5</v>
       </c>
@@ -3355,7 +3355,7 @@
       <c r="E8" s="32"/>
       <c r="F8" s="32"/>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="32"/>
       <c r="B9" s="40" t="s">
         <v>191</v>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="F9" s="32"/>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="32">
         <v>6</v>
       </c>
@@ -3383,7 +3383,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="32"/>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="32">
         <v>7</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="32">
         <v>8</v>
       </c>
@@ -3423,7 +3423,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="32">
         <v>9</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="32">
         <v>10</v>
       </c>
@@ -3459,7 +3459,7 @@
       <c r="E14" s="32"/>
       <c r="F14" s="32"/>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="32">
         <v>11</v>
       </c>
@@ -3479,7 +3479,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="32">
         <v>12</v>
       </c>
@@ -3495,7 +3495,7 @@
       <c r="E16" s="32"/>
       <c r="F16" s="32"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="32">
         <v>13</v>
       </c>
@@ -3511,7 +3511,7 @@
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B18" s="40" t="s">
         <v>216</v>
       </c>

--- a/Data-file.xlsx
+++ b/Data-file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="513" documentId="8_{3CAE69A3-AE5B-4257-93BE-F3BFAEF5261B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F7096FD-64EE-4A16-9CA5-C7A15F64E88C}"/>
+  <xr:revisionPtr revIDLastSave="514" documentId="8_{3CAE69A3-AE5B-4257-93BE-F3BFAEF5261B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CF23B92-5500-4353-94C7-A110D9F7F299}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{8A8E2015-1165-48D9-8246-BE8999149D44}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8A8E2015-1165-48D9-8246-BE8999149D44}"/>
   </bookViews>
   <sheets>
     <sheet name="ACC 3" sheetId="1" r:id="rId1"/>
@@ -2148,11 +2148,11 @@
         <v>297</v>
       </c>
       <c r="C9" s="30">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="D9" s="31">
         <f>D8+C9</f>
-        <v>4826</v>
+        <v>4850</v>
       </c>
     </row>
   </sheetData>

--- a/Data-file.xlsx
+++ b/Data-file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="514" documentId="8_{3CAE69A3-AE5B-4257-93BE-F3BFAEF5261B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CF23B92-5500-4353-94C7-A110D9F7F299}"/>
+  <xr:revisionPtr revIDLastSave="526" documentId="8_{3CAE69A3-AE5B-4257-93BE-F3BFAEF5261B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C5481BE-94AA-4250-BF80-5B8F05B61087}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8A8E2015-1165-48D9-8246-BE8999149D44}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="5" xr2:uid="{8A8E2015-1165-48D9-8246-BE8999149D44}"/>
   </bookViews>
   <sheets>
     <sheet name="ACC 3" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="225">
   <si>
     <t>Month </t>
   </si>
@@ -152,9 +152,6 @@
     <t>RHS CER to ESP </t>
   </si>
   <si>
-    <t>9 / 12 Foundations </t>
-  </si>
-  <si>
     <t>FD/ID/PA 3B cable route-30.06.26/15.07.26/30.07.26/10.08.26/31.08.26/10.09.26/20.09.26/30.09.26</t>
   </si>
   <si>
@@ -188,18 +185,12 @@
     <t>FD-3A</t>
   </si>
   <si>
-    <t>Excavation done</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 30.08.26/30.09.26/15.10.26</t>
   </si>
   <si>
     <t>PA 3A</t>
   </si>
   <si>
-    <t>Raft done. Top deck pending</t>
-  </si>
-  <si>
     <t>10.08.26/31.08.26/10.09.26/24.09.26</t>
   </si>
   <si>
@@ -735,6 +726,12 @@
   </si>
   <si>
     <t>25.10.26/30.11.26</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>10 / 12 Foundations </t>
   </si>
 </sst>
 </file>
@@ -1540,6 +1537,9 @@
         <a:prstGeom prst="trapezoid">
           <a:avLst/>
         </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6"/>
+        </a:solidFill>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -1562,10 +1562,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-IN" sz="2000" b="1"/>
-            <a:t>30-09-26</a:t>
-          </a:r>
+          <a:endParaRPr lang="en-IN" sz="2000" b="1"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1627,7 +1624,7 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="en-IN" sz="2000" b="1"/>
-            <a:t>31-10-26</a:t>
+            <a:t>10-11-26</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1690,7 +1687,7 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="en-IN" sz="2000" b="1"/>
-            <a:t>10-12-26</a:t>
+            <a:t>15-12-26</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2018,14 +2015,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{862506E9-25B6-4CBA-A38B-FADA62B5D706}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2039,7 +2036,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
@@ -2053,7 +2050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A3" s="14" t="s">
         <v>5</v>
       </c>
@@ -2067,7 +2064,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A4" s="16" t="s">
         <v>6</v>
       </c>
@@ -2081,7 +2078,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A5" s="30" t="s">
         <v>7</v>
       </c>
@@ -2095,7 +2092,7 @@
         <v>1815</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A6" s="30" t="s">
         <v>8</v>
       </c>
@@ -2110,7 +2107,7 @@
         <v>2688</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A7" s="30" t="s">
         <v>9</v>
       </c>
@@ -2125,7 +2122,7 @@
         <v>3493</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A8" s="30" t="s">
         <v>10</v>
       </c>
@@ -2140,19 +2137,19 @@
         <v>4615</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A9" s="30" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B9" s="30">
         <v>297</v>
       </c>
       <c r="C9" s="30">
-        <v>235</v>
+        <v>262</v>
       </c>
       <c r="D9" s="31">
         <f>D8+C9</f>
-        <v>4850</v>
+        <v>4877</v>
       </c>
     </row>
   </sheetData>
@@ -2163,13 +2160,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9917535D-21FB-4B58-A8DD-F27CB281E1B3}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.73046875" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -2177,7 +2174,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
@@ -2185,7 +2182,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A3" s="5" t="s">
         <v>15</v>
       </c>
@@ -2193,7 +2190,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="7" t="s">
         <v>17</v>
       </c>
@@ -2201,39 +2198,39 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="30.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="7" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="30.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="5" t="s">
         <v>23</v>
       </c>
@@ -2241,7 +2238,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="7" t="s">
         <v>25</v>
       </c>
@@ -2257,14 +2254,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F89D7ACF-216A-4C43-82E3-F1E9ECF11B39}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="24.5703125" customWidth="1"/>
+    <col min="1" max="1" width="24.59765625" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" customWidth="1"/>
+    <col min="3" max="3" width="41.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="31.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="19" t="s">
         <v>27</v>
       </c>
@@ -2275,100 +2272,100 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="47.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" s="23" t="s">
         <v>30</v>
       </c>
       <c r="B2" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="24" t="s">
+    </row>
+    <row r="3" spans="1:3" ht="47.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A3" s="23" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
+      <c r="B3" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="C3" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="22" t="s">
+    </row>
+    <row r="4" spans="1:3" ht="47.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="47.25" x14ac:dyDescent="0.45">
+      <c r="A5" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="47.25" x14ac:dyDescent="0.45">
+      <c r="A6" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A7" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="28" t="s">
         <v>223</v>
       </c>
-      <c r="C3" s="24" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="28" t="s">
+      <c r="C7" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="28" t="s">
+    </row>
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A8" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="B8" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="28" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="28" t="s">
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A9" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B9" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="28" t="s">
+    </row>
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A10" s="28" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="28" t="s">
+      <c r="B10" s="28" t="s">
         <v>48</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" s="28" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="28" t="s">
-        <v>51</v>
       </c>
       <c r="C10" s="29"/>
     </row>
@@ -2380,25 +2377,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73E19115-1CD0-4934-BDF4-4937A2D87F36}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
         <v>52</v>
-      </c>
-      <c r="B1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>55</v>
       </c>
       <c r="B2">
         <v>1448.3</v>
@@ -2407,9 +2404,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B3">
         <v>573.82000000000005</v>
@@ -2427,60 +2424,60 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73BDED7B-F217-445A-9C06-91034F503C5D}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="27.7109375" customWidth="1"/>
-    <col min="2" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" customWidth="1"/>
+    <col min="1" max="1" width="27.73046875" customWidth="1"/>
+    <col min="2" max="3" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="28.15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="9" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" s="10" t="s">
         <v>57</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>60</v>
       </c>
       <c r="B2" s="11">
         <v>1200</v>
       </c>
       <c r="C2" s="11">
-        <v>643</v>
+        <v>706</v>
       </c>
       <c r="D2" s="11">
         <f>B2-C2</f>
-        <v>557</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="10" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B3" s="11">
         <v>400</v>
       </c>
       <c r="C3" s="11">
-        <v>231</v>
+        <v>271</v>
       </c>
       <c r="D3" s="11">
         <f t="shared" ref="D3:D8" si="0">B3-C3</f>
-        <v>169</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="10" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B4" s="12">
         <v>400</v>
@@ -2493,24 +2490,24 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="10" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B5" s="12">
         <v>400</v>
       </c>
       <c r="C5" s="12">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D5" s="11">
         <f t="shared" si="0"/>
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="10" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6" s="12">
         <v>250</v>
@@ -2523,9 +2520,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="10" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B7" s="12">
         <v>100</v>
@@ -2538,9 +2535,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="10" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B8" s="12">
         <v>100</v>
@@ -2553,9 +2550,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="10" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B9" s="12">
         <f>SUM(B2:B8)</f>
@@ -2563,11 +2560,11 @@
       </c>
       <c r="C9" s="12">
         <f>SUM(C2:C8)</f>
-        <v>1807</v>
+        <v>1914</v>
       </c>
       <c r="D9" s="12">
         <f>SUM(D2:D8)</f>
-        <v>1043</v>
+        <v>936</v>
       </c>
     </row>
   </sheetData>
@@ -2578,7 +2575,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{937E703F-939A-4FE6-A55F-3284F68BDE73}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2588,622 +2585,622 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC87E3DB-D54A-4C9B-8DF9-428C70D3A6F3}">
   <dimension ref="A1:W303"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.73046875" customWidth="1"/>
+    <col min="5" max="5" width="14.73046875" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="23" max="23" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="2.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="39" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="39" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="E1" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="F1" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="G1" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="H1" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="37" t="s">
+      <c r="I1" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="G1" s="37" t="s">
+      <c r="J1" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="H1" s="37" t="s">
+      <c r="K1" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="I1" s="39" t="s">
+      <c r="L1" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="J1" s="39" t="s">
+    </row>
+    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A2" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="K1" s="39" t="s">
+      <c r="B2" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="L1" s="39" t="s">
+      <c r="C2" s="35" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
+      <c r="D2" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="E2" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="F2" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="D2" s="35" t="s">
+      <c r="G2" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="35" t="s">
+      <c r="H2" s="35" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A3" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="F2" s="35" t="s">
+      <c r="B3" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="G2" s="35" t="s">
+      <c r="C3" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="H2" s="35" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
+      <c r="D3" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="F3" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="H3" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="D3" s="35" t="s">
-        <v>85</v>
-      </c>
-      <c r="E3" s="35" t="s">
+    </row>
+    <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A4" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="35" t="s">
         <v>90</v>
       </c>
-      <c r="F3" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="G3" s="35" t="s">
+      <c r="C4" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="H3" s="35" t="s">
+      <c r="D4" s="35" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="35" t="s">
+      <c r="E4" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="F4" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="G4" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="H4" s="35" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A5" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="F5" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="G5" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="H5" s="35" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A6" s="35" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="F6" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="H6" s="35" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A7" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="E7" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="F7" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="G7" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="H7" s="35" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A8" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="B4" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="C4" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="D4" s="35" t="s">
+      <c r="B8" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>115</v>
+      </c>
+      <c r="G8" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="H8" s="35" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A9" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>119</v>
+      </c>
+      <c r="F9" s="35" t="s">
+        <v>119</v>
+      </c>
+      <c r="G9" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="H9" s="35" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A10" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="E10" s="35" t="s">
+        <v>115</v>
+      </c>
+      <c r="F10" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="G10" s="35" t="s">
+        <v>115</v>
+      </c>
+      <c r="H10" s="35" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A11" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="C11" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="D11" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="E11" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="F11" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="G11" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="H11" s="38" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A12" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>129</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="F12" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="G12" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="H12" s="38" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A13" s="35" t="s">
+        <v>119</v>
+      </c>
+      <c r="B13" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="D13" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="H13" s="38" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A14" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="D14" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="E14" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="G14" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" s="35" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A15" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="D15" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="E15" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="F15" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="G15" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="H15" s="35" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A16" s="35" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>137</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="D16" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" s="38" t="s">
+        <v>139</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="H16" s="38" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A17" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="C17" s="38" t="s">
+        <v>141</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="E17" s="38" t="s">
+        <v>143</v>
+      </c>
+      <c r="F17" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="G17" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="H17" s="38" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A18" s="35" t="s">
+        <v>146</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" s="35" t="s">
+        <v>148</v>
+      </c>
+      <c r="D18" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="E18" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="F18" s="35" t="s">
+        <v>115</v>
+      </c>
+      <c r="G18" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="H18" s="35" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A19" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="B19" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="C19" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="D19" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="E19" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="F19" s="35" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="35" t="s">
-        <v>96</v>
-      </c>
-      <c r="F4" s="35" t="s">
-        <v>96</v>
-      </c>
-      <c r="G4" s="35" t="s">
-        <v>86</v>
-      </c>
-      <c r="H4" s="35" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="35" t="s">
-        <v>98</v>
-      </c>
-      <c r="B5" s="35" t="s">
-        <v>99</v>
-      </c>
-      <c r="C5" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="D5" s="35" t="s">
-        <v>101</v>
-      </c>
-      <c r="E5" s="35" t="s">
-        <v>102</v>
-      </c>
-      <c r="F5" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="G5" s="35" t="s">
-        <v>83</v>
-      </c>
-      <c r="H5" s="35" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="B6" s="35" t="s">
-        <v>106</v>
-      </c>
-      <c r="C6" s="35" t="s">
-        <v>107</v>
-      </c>
-      <c r="D6" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="E6" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="F6" s="35" t="s">
-        <v>80</v>
-      </c>
-      <c r="G6" s="35" t="s">
+      <c r="H19" s="35" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A20" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="B20" s="35" t="s">
+        <v>152</v>
+      </c>
+      <c r="C20" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="D20" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="E20" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="G20" s="35" t="s">
+        <v>115</v>
+      </c>
+      <c r="H20" s="35" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A21" s="35" t="s">
         <v>110</v>
       </c>
-      <c r="H6" s="35" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="B7" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="C7" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="D7" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="E7" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="F7" s="35" t="s">
-        <v>98</v>
-      </c>
-      <c r="G7" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="H7" s="35" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="B8" s="35" t="s">
+      <c r="B21" s="35" t="s">
+        <v>154</v>
+      </c>
+      <c r="C21" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="D21" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="E21" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="F21" s="35" t="s">
+        <v>156</v>
+      </c>
+      <c r="G21" s="35" t="s">
         <v>115</v>
       </c>
-      <c r="C8" s="35" t="s">
-        <v>116</v>
-      </c>
-      <c r="D8" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="E8" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="F8" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="G8" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="H8" s="35" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="35" t="s">
-        <v>92</v>
-      </c>
-      <c r="B9" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="C9" s="35" t="s">
-        <v>120</v>
-      </c>
-      <c r="D9" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="E9" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="F9" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="G9" s="35" t="s">
-        <v>92</v>
-      </c>
-      <c r="H9" s="35" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="35" t="s">
-        <v>124</v>
-      </c>
-      <c r="B10" s="35" t="s">
-        <v>125</v>
-      </c>
-      <c r="C10" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="D10" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="E10" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="F10" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="G10" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="H10" s="35" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="35" t="s">
+      <c r="H21" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="B11" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>129</v>
-      </c>
-      <c r="D11" s="38" t="s">
-        <v>130</v>
-      </c>
-      <c r="E11" s="38" t="s">
-        <v>118</v>
-      </c>
-      <c r="F11" s="38" t="s">
-        <v>130</v>
-      </c>
-      <c r="G11" s="38" t="s">
-        <v>118</v>
-      </c>
-      <c r="H11" s="38" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="B12" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>132</v>
-      </c>
-      <c r="D12" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" s="38" t="s">
-        <v>118</v>
-      </c>
-      <c r="F12" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="G12" s="38" t="s">
-        <v>118</v>
-      </c>
-      <c r="H12" s="38" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="B13" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>134</v>
-      </c>
-      <c r="D13" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="E13" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="F13" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="G13" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="H13" s="38" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="35" t="s">
-        <v>85</v>
-      </c>
-      <c r="B14" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="C14" s="35" t="s">
-        <v>136</v>
-      </c>
-      <c r="D14" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="E14" s="35" t="s">
-        <v>86</v>
-      </c>
-      <c r="F14" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="G14" s="35" t="s">
-        <v>86</v>
-      </c>
-      <c r="H14" s="35" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="35" t="s">
-        <v>86</v>
-      </c>
-      <c r="B15" s="35" t="s">
-        <v>137</v>
-      </c>
-      <c r="C15" s="35" t="s">
-        <v>138</v>
-      </c>
-      <c r="D15" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="E15" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="F15" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="G15" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="H15" s="35" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="B16" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>141</v>
-      </c>
-      <c r="D16" s="38" t="s">
-        <v>103</v>
-      </c>
-      <c r="E16" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="F16" s="38" t="s">
-        <v>142</v>
-      </c>
-      <c r="G16" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="H16" s="38" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="35" t="s">
-        <v>123</v>
-      </c>
-      <c r="B17" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>144</v>
-      </c>
-      <c r="D17" s="38" t="s">
-        <v>145</v>
-      </c>
-      <c r="E17" s="38" t="s">
-        <v>146</v>
-      </c>
-      <c r="F17" s="38" t="s">
-        <v>147</v>
-      </c>
-      <c r="G17" s="38" t="s">
-        <v>113</v>
-      </c>
-      <c r="H17" s="38" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="B18" s="35" t="s">
-        <v>150</v>
-      </c>
-      <c r="C18" s="35" t="s">
-        <v>151</v>
-      </c>
-      <c r="D18" s="35" t="s">
-        <v>124</v>
-      </c>
-      <c r="E18" s="35" t="s">
-        <v>124</v>
-      </c>
-      <c r="F18" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="G18" s="35" t="s">
-        <v>124</v>
-      </c>
-      <c r="H18" s="35" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="B19" s="35" t="s">
-        <v>152</v>
-      </c>
-      <c r="C19" s="35" t="s">
-        <v>153</v>
-      </c>
-      <c r="D19" s="35" t="s">
-        <v>154</v>
-      </c>
-      <c r="E19" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="F19" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="G19" s="35" t="s">
-        <v>98</v>
-      </c>
-      <c r="H19" s="35" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="35" t="s">
-        <v>154</v>
-      </c>
-      <c r="B20" s="35" t="s">
-        <v>155</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>156</v>
-      </c>
-      <c r="D20" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="E20" s="35" t="s">
-        <v>80</v>
-      </c>
-      <c r="F20" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="G20" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="H20" s="35" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="B21" s="35" t="s">
-        <v>157</v>
-      </c>
-      <c r="C21" s="35" t="s">
-        <v>158</v>
-      </c>
-      <c r="D21" s="35" t="s">
-        <v>130</v>
-      </c>
-      <c r="E21" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="F21" s="35" t="s">
-        <v>159</v>
-      </c>
-      <c r="G21" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="H21" s="35" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A22" s="36"/>
       <c r="B22" s="36"/>
       <c r="C22" s="37" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D22" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="F22" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="G22" s="37" t="s">
         <v>160</v>
       </c>
-      <c r="E22" s="37" t="s">
+      <c r="H22" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="F22" s="37" t="s">
-        <v>162</v>
-      </c>
-      <c r="G22" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="H22" s="37" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:8" ht="15.75" hidden="1" x14ac:dyDescent="0.5">
       <c r="A23" s="33"/>
       <c r="B23" s="33"/>
       <c r="C23" s="34" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D23" s="33"/>
       <c r="E23" s="34" t="s">
+        <v>163</v>
+      </c>
+      <c r="F23" s="34" t="s">
+        <v>164</v>
+      </c>
+      <c r="G23" s="34" t="s">
+        <v>165</v>
+      </c>
+      <c r="H23" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="F23" s="34" t="s">
+    </row>
+    <row r="303" spans="23:23" x14ac:dyDescent="0.45">
+      <c r="W303" t="s">
         <v>167</v>
-      </c>
-      <c r="G23" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="H23" s="34" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="303" spans="23:23" x14ac:dyDescent="0.25">
-      <c r="W303" t="s">
-        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -3214,36 +3211,36 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{742D201E-24F7-4C61-8302-831552FAC820}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="43" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="D1" s="43" t="s">
         <v>171</v>
       </c>
-      <c r="B1" s="43" t="s">
+      <c r="E1" s="43" t="s">
         <v>172</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="F1" s="43" t="s">
         <v>173</v>
       </c>
-      <c r="D1" s="43" t="s">
-        <v>174</v>
-      </c>
-      <c r="E1" s="43" t="s">
-        <v>175</v>
-      </c>
-      <c r="F1" s="43" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="44"/>
       <c r="B2" s="44"/>
       <c r="C2" s="44"/>
@@ -3251,7 +3248,7 @@
       <c r="E2" s="44"/>
       <c r="F2" s="44"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="44"/>
       <c r="B3" s="44"/>
       <c r="C3" s="44"/>
@@ -3259,95 +3256,95 @@
       <c r="E3" s="44"/>
       <c r="F3" s="44"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="32">
         <v>1</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D4" s="32">
         <v>11</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="32">
         <v>2</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D5" s="32">
         <v>11</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="32">
         <v>3</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D6" s="32">
         <v>11</v>
       </c>
       <c r="E6" s="32" t="s">
+        <v>180</v>
+      </c>
+      <c r="F6" s="32" t="s">
         <v>183</v>
       </c>
-      <c r="F6" s="32" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="32">
         <v>4</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D7" s="32">
         <v>11</v>
       </c>
       <c r="E7" s="32" t="s">
+        <v>180</v>
+      </c>
+      <c r="F7" s="32" t="s">
         <v>183</v>
       </c>
-      <c r="F7" s="32" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="32">
         <v>5</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D8" s="32">
         <v>11</v>
@@ -3355,27 +3352,27 @@
       <c r="E8" s="32"/>
       <c r="F8" s="32"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="32"/>
       <c r="B9" s="40" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C9" s="41"/>
       <c r="D9" s="42"/>
       <c r="E9" s="32" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F9" s="32"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="32">
         <v>6</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D10" s="32">
         <v>3.3</v>
@@ -3383,75 +3380,75 @@
       <c r="E10" s="32"/>
       <c r="F10" s="32"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="32">
         <v>7</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D11" s="32">
         <v>3.3</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F11" s="32" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="32">
         <v>8</v>
       </c>
       <c r="B12" s="32" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D12" s="32">
         <v>3.3</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F12" s="32" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="32">
         <v>9</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D13" s="32">
         <v>3.3</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F13" s="32" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" s="32">
         <v>10</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D14" s="32">
         <v>3.3</v>
@@ -3459,35 +3456,35 @@
       <c r="E14" s="32"/>
       <c r="F14" s="32"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="32">
         <v>11</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D15" s="32">
         <v>3.3</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F15" s="32" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="32">
         <v>12</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D16" s="32">
         <v>3.3</v>
@@ -3495,15 +3492,15 @@
       <c r="E16" s="32"/>
       <c r="F16" s="32"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" s="32">
         <v>13</v>
       </c>
       <c r="B17" s="32" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D17" s="32">
         <v>3.3</v>
@@ -3511,14 +3508,14 @@
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B18" s="40" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C18" s="41"/>
       <c r="D18" s="42"/>
       <c r="E18" s="32" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F18" s="32"/>
     </row>

--- a/Data-file.xlsx
+++ b/Data-file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="526" documentId="8_{3CAE69A3-AE5B-4257-93BE-F3BFAEF5261B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C5481BE-94AA-4250-BF80-5B8F05B61087}"/>
+  <xr:revisionPtr revIDLastSave="551" documentId="8_{3CAE69A3-AE5B-4257-93BE-F3BFAEF5261B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D82F54B7-FE99-4925-89B3-E2A1C7CFFBB6}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="5" xr2:uid="{8A8E2015-1165-48D9-8246-BE8999149D44}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{8A8E2015-1165-48D9-8246-BE8999149D44}"/>
   </bookViews>
   <sheets>
     <sheet name="ACC 3" sheetId="1" r:id="rId1"/>
@@ -152,15 +152,9 @@
     <t>RHS CER to ESP </t>
   </si>
   <si>
-    <t>FD/ID/PA 3B cable route-30.06.26/15.07.26/30.07.26/10.08.26/31.08.26/10.09.26/20.09.26/30.09.26</t>
-  </si>
-  <si>
     <t>LHS CER to ESP </t>
   </si>
   <si>
-    <t>ID3A cable route-30.06.26/15.07.26/30.07.26/14.08.26/05.09.26/20.09.26/30.09.26</t>
-  </si>
-  <si>
     <t>CER to Boiler </t>
   </si>
   <si>
@@ -173,9 +167,6 @@
     <t>3/8 Foundations </t>
   </si>
   <si>
-    <t>ESP CR to ESP cablings-30.07.26/20.08.26/10.09.26/15.09.26/30.09.26</t>
-  </si>
-  <si>
     <t>ESP to ESP Control Room (RHS) - RVPR</t>
   </si>
   <si>
@@ -185,9 +176,6 @@
     <t>FD-3A</t>
   </si>
   <si>
-    <t xml:space="preserve"> 30.08.26/30.09.26/15.10.26</t>
-  </si>
-  <si>
     <t>PA 3A</t>
   </si>
   <si>
@@ -599,9 +587,6 @@
     <t>14425 KW</t>
   </si>
   <si>
-    <t>15.10.26</t>
-  </si>
-  <si>
     <t>FD FAN</t>
   </si>
   <si>
@@ -641,24 +626,12 @@
     <t>930 KW</t>
   </si>
   <si>
-    <t>25.09.26/10.10.26/20.10.26</t>
-  </si>
-  <si>
-    <t>05.10.26/20.10.26/25.10.26</t>
-  </si>
-  <si>
     <t>ECW PUMP (TG)</t>
   </si>
   <si>
     <t>200 KW</t>
   </si>
   <si>
-    <t>10.10.26/20.10.26</t>
-  </si>
-  <si>
-    <t>10.10.26/15.10.26/25.10.26</t>
-  </si>
-  <si>
     <t>ACW PUMP</t>
   </si>
   <si>
@@ -668,9 +641,6 @@
     <t>BOP Board</t>
   </si>
   <si>
-    <t>15.09.26/25.09.26/05.10.26</t>
-  </si>
-  <si>
     <t>HOGGING PUMP</t>
   </si>
   <si>
@@ -683,9 +653,6 @@
     <t>160 KW</t>
   </si>
   <si>
-    <t>10.10.26/15.10.26/31.10.26</t>
-  </si>
-  <si>
     <t>DRIP PUMP</t>
   </si>
   <si>
@@ -719,9 +686,6 @@
     <t>31.10.26/25.11.26/10.12.27</t>
   </si>
   <si>
-    <t>4 / 7 Foundations </t>
-  </si>
-  <si>
     <t>Capex till Sep end</t>
   </si>
   <si>
@@ -732,6 +696,42 @@
   </si>
   <si>
     <t>10 / 12 Foundations </t>
+  </si>
+  <si>
+    <t>5 / 7 Foundations </t>
+  </si>
+  <si>
+    <t>FD/ID/PA 3B cable route-30.06.26/15.07.26/30.07.26/10.08.26/31.08.26/10.09.26/20.09.26/30.09.26/25.10.26</t>
+  </si>
+  <si>
+    <t>ID3A cable route-30.06.26/15.07.26/30.07.26/14.08.26/05.09.26/20.09.26/30.09.26/20.10.26 (last one after centre section removal)</t>
+  </si>
+  <si>
+    <t>ESP CR to ESP cablings-30.07.26/20.08.26/10.09.26/15.09.26/30.09.26/31.10.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 30.08.26/30.09.26/15.10.26/30.10.26</t>
+  </si>
+  <si>
+    <t>15.10.26/25.10.26</t>
+  </si>
+  <si>
+    <t>10.10.26/20.10.26/04.11.26</t>
+  </si>
+  <si>
+    <t>25.09.26/10.10.26/20.10.26/04.11.26</t>
+  </si>
+  <si>
+    <t>05.10.26/20.10.26/25.10.26/20.11.26</t>
+  </si>
+  <si>
+    <t>10.10.26/15.10.26/25.10.26/10.11.26</t>
+  </si>
+  <si>
+    <t>15.09.26/25.09.26/05.10.26/15.10.26</t>
+  </si>
+  <si>
+    <t>10.10.26/15.10.26/31.10.26/20.11.26</t>
   </si>
 </sst>
 </file>
@@ -1697,6 +1697,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2015,14 +2019,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{862506E9-25B6-4CBA-A38B-FADA62B5D706}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:4" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2036,7 +2040,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
@@ -2050,7 +2054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>5</v>
       </c>
@@ -2064,7 +2068,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>6</v>
       </c>
@@ -2078,7 +2082,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="30" t="s">
         <v>7</v>
       </c>
@@ -2092,7 +2096,7 @@
         <v>1815</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="30" t="s">
         <v>8</v>
       </c>
@@ -2107,7 +2111,7 @@
         <v>2688</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="30" t="s">
         <v>9</v>
       </c>
@@ -2122,7 +2126,7 @@
         <v>3493</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="30" t="s">
         <v>10</v>
       </c>
@@ -2137,19 +2141,19 @@
         <v>4615</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="30" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="B9" s="30">
         <v>297</v>
       </c>
       <c r="C9" s="30">
-        <v>262</v>
+        <v>657</v>
       </c>
       <c r="D9" s="31">
         <f>D8+C9</f>
-        <v>4877</v>
+        <v>5272</v>
       </c>
     </row>
   </sheetData>
@@ -2160,13 +2164,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9917535D-21FB-4B58-A8DD-F27CB281E1B3}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.73046875" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -2174,7 +2178,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
@@ -2182,7 +2186,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>15</v>
       </c>
@@ -2190,7 +2194,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>17</v>
       </c>
@@ -2198,39 +2202,39 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30.4" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="30.4" thickBot="1" x14ac:dyDescent="0.5">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>23</v>
       </c>
@@ -2238,7 +2242,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>25</v>
       </c>
@@ -2254,14 +2258,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F89D7ACF-216A-4C43-82E3-F1E9ECF11B39}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.59765625" customWidth="1"/>
+    <col min="1" max="1" width="24.5703125" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="41.1328125" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="31.9" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>27</v>
       </c>
@@ -2272,100 +2276,100 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="47.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:3" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>30</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="C2" s="24" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="23" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="47.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="23" t="s">
+      <c r="B3" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="22" t="s">
-        <v>220</v>
-      </c>
-      <c r="C3" s="24" t="s">
+      <c r="B4" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="24" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="47.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="23" t="s">
+    <row r="5" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="24" t="s">
+      <c r="B5" s="26" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="47.25" x14ac:dyDescent="0.45">
-      <c r="A5" s="25" t="s">
+      <c r="C5" s="27" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B6" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="27" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="28" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="47.25" x14ac:dyDescent="0.45">
-      <c r="A6" s="28" t="s">
+      <c r="B7" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="28" t="s">
+      <c r="B8" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="28" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A7" s="28" t="s">
+    <row r="9" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="28" t="s">
-        <v>223</v>
-      </c>
-      <c r="C7" s="28" t="s">
+      <c r="B9" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="28" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A8" s="28" t="s">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="28" t="s">
+      <c r="B10" s="28" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A9" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="28" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A10" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="28" t="s">
-        <v>48</v>
       </c>
       <c r="C10" s="29"/>
     </row>
@@ -2377,25 +2381,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73E19115-1CD0-4934-BDF4-4937A2D87F36}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B2">
         <v>1448.3</v>
@@ -2404,9 +2408,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="B3">
         <v>573.82000000000005</v>
@@ -2424,30 +2428,30 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73BDED7B-F217-445A-9C06-91034F503C5D}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.73046875" customWidth="1"/>
-    <col min="2" max="3" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.265625" customWidth="1"/>
+    <col min="1" max="1" width="27.7109375" customWidth="1"/>
+    <col min="2" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.15" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A2" s="10" t="s">
-        <v>57</v>
       </c>
       <c r="B2" s="11">
         <v>1200</v>
@@ -2460,9 +2464,9 @@
         <v>494</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B3" s="11">
         <v>400</v>
@@ -2475,24 +2479,24 @@
         <v>129</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B4" s="12">
         <v>400</v>
       </c>
       <c r="C4" s="12">
-        <v>352</v>
+        <v>266</v>
       </c>
       <c r="D4" s="11">
         <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B5" s="12">
         <v>400</v>
@@ -2505,54 +2509,54 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B6" s="12">
         <v>250</v>
       </c>
       <c r="C6" s="12">
-        <v>137</v>
+        <v>180</v>
       </c>
       <c r="D6" s="11">
         <f t="shared" si="0"/>
-        <v>113</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B7" s="12">
         <v>100</v>
       </c>
       <c r="C7" s="12">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D7" s="11">
         <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B8" s="12">
         <v>100</v>
       </c>
       <c r="C8" s="12">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D8" s="11">
         <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B9" s="12">
         <f>SUM(B2:B8)</f>
@@ -2560,11 +2564,11 @@
       </c>
       <c r="C9" s="12">
         <f>SUM(C2:C8)</f>
-        <v>1914</v>
+        <v>1885</v>
       </c>
       <c r="D9" s="12">
         <f>SUM(D2:D8)</f>
-        <v>936</v>
+        <v>965</v>
       </c>
     </row>
   </sheetData>
@@ -2575,7 +2579,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{937E703F-939A-4FE6-A55F-3284F68BDE73}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2585,622 +2589,622 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC87E3DB-D54A-4C9B-8DF9-428C70D3A6F3}">
   <dimension ref="A1:W303"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.73046875" customWidth="1"/>
-    <col min="5" max="5" width="14.73046875" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="23" max="23" width="2.73046875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="2.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="39" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" s="39" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="F1" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="G1" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="H1" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="I1" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="37" t="s">
+      <c r="J1" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="G1" s="37" t="s">
+      <c r="K1" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="H1" s="37" t="s">
+      <c r="L1" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="I1" s="39" t="s">
+    </row>
+    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="J1" s="39" t="s">
+      <c r="B2" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="K1" s="39" t="s">
+      <c r="C2" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="L1" s="39" t="s">
+      <c r="D2" s="35" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A2" s="35" t="s">
+      <c r="E2" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="F2" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="G2" s="35" t="s">
         <v>79</v>
       </c>
-      <c r="D2" s="35" t="s">
+      <c r="H2" s="35" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="E2" s="35" t="s">
+      <c r="B3" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="F2" s="35" t="s">
+      <c r="C3" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="G2" s="35" t="s">
+      <c r="D3" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="H2" s="35" t="s">
+      <c r="F3" s="35" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A3" s="35" t="s">
+      <c r="G3" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="H3" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="35" t="s">
+    </row>
+    <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="D3" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="E3" s="35" t="s">
+      <c r="C4" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="F3" s="35" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="35" t="s">
+      <c r="D4" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="H3" s="35" t="s">
+      <c r="E4" s="35" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A4" s="35" t="s">
+      <c r="F4" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="G4" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="H4" s="35" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="F5" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="G5" s="35" t="s">
+        <v>76</v>
+      </c>
+      <c r="H5" s="35" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="35" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>102</v>
+      </c>
+      <c r="F6" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="G6" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="H6" s="35" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="B4" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="C4" s="35" t="s">
+      <c r="B7" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="E7" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="F7" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="35" t="s">
-        <v>92</v>
-      </c>
-      <c r="E4" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="F4" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="G4" s="35" t="s">
+      <c r="G7" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="H7" s="35" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="H4" s="35" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A5" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="B5" s="35" t="s">
+      <c r="B8" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="G8" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="H8" s="35" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="35" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>115</v>
+      </c>
+      <c r="F9" s="35" t="s">
+        <v>115</v>
+      </c>
+      <c r="G9" s="35" t="s">
+        <v>85</v>
+      </c>
+      <c r="H9" s="35" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>119</v>
+      </c>
+      <c r="D10" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="E10" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="F10" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="G10" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="H10" s="35" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="D11" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="E11" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="F11" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="G11" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="H11" s="38" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>125</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="F12" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="H12" s="38" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="35" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="C13" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="D13" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="G13" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="H13" s="38" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="D14" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="F14" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="G14" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="H14" s="35" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="D15" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="E15" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="F15" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="G15" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="H15" s="35" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>134</v>
+      </c>
+      <c r="D16" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="C5" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="D5" s="35" t="s">
-        <v>98</v>
-      </c>
-      <c r="E5" s="35" t="s">
-        <v>99</v>
-      </c>
-      <c r="F5" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="G5" s="35" t="s">
-        <v>80</v>
-      </c>
-      <c r="H5" s="35" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A6" s="35" t="s">
-        <v>102</v>
-      </c>
-      <c r="B6" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="C6" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="D6" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="E6" s="35" t="s">
+      <c r="E16" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" s="38" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="C17" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="E17" s="38" t="s">
+        <v>139</v>
+      </c>
+      <c r="F17" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="G17" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="F6" s="35" t="s">
+      <c r="H17" s="38" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="C18" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="D18" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="F18" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="G18" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="H18" s="35" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="C19" s="35" t="s">
+        <v>146</v>
+      </c>
+      <c r="D19" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="E19" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="F19" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="G6" s="35" t="s">
-        <v>107</v>
-      </c>
-      <c r="H6" s="35" t="s">
+      <c r="G19" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H19" s="35" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="B20" s="35" t="s">
+        <v>148</v>
+      </c>
+      <c r="C20" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="D20" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" s="35" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A7" s="35" t="s">
-        <v>88</v>
-      </c>
-      <c r="B7" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="E7" s="35" t="s">
+      <c r="G20" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="F7" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="G7" s="35" t="s">
+      <c r="H20" s="35" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="C21" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="D21" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="E21" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="F21" s="35" t="s">
+        <v>152</v>
+      </c>
+      <c r="G21" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="H7" s="35" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A8" s="35" t="s">
-        <v>87</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="C8" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="D8" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="E8" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="F8" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="G8" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="H8" s="35" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A9" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="B9" s="35" t="s">
-        <v>116</v>
-      </c>
-      <c r="C9" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="D9" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="E9" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="F9" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="G9" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="H9" s="35" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A10" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="B10" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="C10" s="35" t="s">
+      <c r="H21" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="D10" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="E10" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="F10" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="G10" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="H10" s="35" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A11" s="35" t="s">
-        <v>124</v>
-      </c>
-      <c r="B11" s="35" t="s">
-        <v>125</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>126</v>
-      </c>
-      <c r="D11" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="E11" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="F11" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="G11" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="H11" s="38" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A12" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="B12" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>129</v>
-      </c>
-      <c r="D12" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="E12" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="F12" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="H12" s="38" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A13" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="B13" s="35" t="s">
-        <v>130</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>131</v>
-      </c>
-      <c r="D13" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="E13" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="F13" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="G13" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="H13" s="38" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A14" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="B14" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="C14" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="D14" s="35" t="s">
-        <v>107</v>
-      </c>
-      <c r="E14" s="35" t="s">
-        <v>83</v>
-      </c>
-      <c r="F14" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="G14" s="35" t="s">
-        <v>83</v>
-      </c>
-      <c r="H14" s="35" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A15" s="35" t="s">
-        <v>83</v>
-      </c>
-      <c r="B15" s="35" t="s">
-        <v>134</v>
-      </c>
-      <c r="C15" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="D15" s="35" t="s">
-        <v>136</v>
-      </c>
-      <c r="E15" s="35" t="s">
-        <v>87</v>
-      </c>
-      <c r="F15" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="G15" s="35" t="s">
-        <v>87</v>
-      </c>
-      <c r="H15" s="35" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A16" s="35" t="s">
-        <v>81</v>
-      </c>
-      <c r="B16" s="35" t="s">
-        <v>137</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>138</v>
-      </c>
-      <c r="D16" s="38" t="s">
-        <v>100</v>
-      </c>
-      <c r="E16" s="38" t="s">
-        <v>82</v>
-      </c>
-      <c r="F16" s="38" t="s">
-        <v>139</v>
-      </c>
-      <c r="G16" s="38" t="s">
-        <v>82</v>
-      </c>
-      <c r="H16" s="38" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A17" s="35" t="s">
-        <v>120</v>
-      </c>
-      <c r="B17" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>141</v>
-      </c>
-      <c r="D17" s="38" t="s">
-        <v>142</v>
-      </c>
-      <c r="E17" s="38" t="s">
-        <v>143</v>
-      </c>
-      <c r="F17" s="38" t="s">
-        <v>144</v>
-      </c>
-      <c r="G17" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="H17" s="38" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A18" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="B18" s="35" t="s">
-        <v>147</v>
-      </c>
-      <c r="C18" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="D18" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="E18" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="F18" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="G18" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="H18" s="35" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A19" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="B19" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="C19" s="35" t="s">
-        <v>150</v>
-      </c>
-      <c r="D19" s="35" t="s">
-        <v>151</v>
-      </c>
-      <c r="E19" s="35" t="s">
-        <v>88</v>
-      </c>
-      <c r="F19" s="35" t="s">
-        <v>81</v>
-      </c>
-      <c r="G19" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="H19" s="35" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A20" s="35" t="s">
-        <v>151</v>
-      </c>
-      <c r="B20" s="35" t="s">
-        <v>152</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>153</v>
-      </c>
-      <c r="D20" s="35" t="s">
-        <v>87</v>
-      </c>
-      <c r="E20" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="F20" s="35" t="s">
-        <v>88</v>
-      </c>
-      <c r="G20" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="H20" s="35" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A21" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="B21" s="35" t="s">
-        <v>154</v>
-      </c>
-      <c r="C21" s="35" t="s">
-        <v>155</v>
-      </c>
-      <c r="D21" s="35" t="s">
-        <v>127</v>
-      </c>
-      <c r="E21" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="F21" s="35" t="s">
-        <v>156</v>
-      </c>
-      <c r="G21" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="H21" s="35" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
+    </row>
+    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="36"/>
       <c r="B22" s="36"/>
       <c r="C22" s="37" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D22" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="F22" s="37" t="s">
+        <v>155</v>
+      </c>
+      <c r="G22" s="37" t="s">
+        <v>156</v>
+      </c>
+      <c r="H22" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="E22" s="37" t="s">
-        <v>158</v>
-      </c>
-      <c r="F22" s="37" t="s">
-        <v>159</v>
-      </c>
-      <c r="G22" s="37" t="s">
-        <v>160</v>
-      </c>
-      <c r="H22" s="37" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="15.75" hidden="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="23" spans="1:8" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="33"/>
       <c r="B23" s="33"/>
       <c r="C23" s="34" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D23" s="33"/>
       <c r="E23" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="F23" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="G23" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="H23" s="34" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="303" spans="23:23" x14ac:dyDescent="0.25">
+      <c r="W303" t="s">
         <v>163</v>
-      </c>
-      <c r="F23" s="34" t="s">
-        <v>164</v>
-      </c>
-      <c r="G23" s="34" t="s">
-        <v>165</v>
-      </c>
-      <c r="H23" s="34" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="303" spans="23:23" x14ac:dyDescent="0.45">
-      <c r="W303" t="s">
-        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -3211,36 +3215,36 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{742D201E-24F7-4C61-8302-831552FAC820}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="43" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="E1" s="43" t="s">
         <v>168</v>
       </c>
-      <c r="B1" s="43" t="s">
+      <c r="F1" s="43" t="s">
         <v>169</v>
       </c>
-      <c r="C1" s="43" t="s">
-        <v>170</v>
-      </c>
-      <c r="D1" s="43" t="s">
-        <v>171</v>
-      </c>
-      <c r="E1" s="43" t="s">
-        <v>172</v>
-      </c>
-      <c r="F1" s="43" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="44"/>
       <c r="B2" s="44"/>
       <c r="C2" s="44"/>
@@ -3248,7 +3252,7 @@
       <c r="E2" s="44"/>
       <c r="F2" s="44"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="44"/>
       <c r="B3" s="44"/>
       <c r="C3" s="44"/>
@@ -3256,95 +3260,95 @@
       <c r="E3" s="44"/>
       <c r="F3" s="44"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="32">
         <v>1</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D4" s="32">
         <v>11</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="32">
         <v>2</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D5" s="32">
         <v>11</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="32">
         <v>3</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D6" s="32">
         <v>11</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="F6" s="32" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="32">
         <v>4</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D7" s="32">
         <v>11</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="F7" s="32" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="32">
         <v>5</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D8" s="32">
         <v>11</v>
@@ -3352,27 +3356,27 @@
       <c r="E8" s="32"/>
       <c r="F8" s="32"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="32"/>
       <c r="B9" s="40" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C9" s="41"/>
       <c r="D9" s="42"/>
       <c r="E9" s="32" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="F9" s="32"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="32">
         <v>6</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D10" s="32">
         <v>3.3</v>
@@ -3380,75 +3384,75 @@
       <c r="E10" s="32"/>
       <c r="F10" s="32"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="32">
         <v>7</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D11" s="32">
         <v>3.3</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="F11" s="32" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="32">
         <v>8</v>
       </c>
       <c r="B12" s="32" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="D12" s="32">
         <v>3.3</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="F12" s="32" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="32">
         <v>9</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="D13" s="32">
         <v>3.3</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="F13" s="32" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="32">
         <v>10</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="D14" s="32">
         <v>3.3</v>
@@ -3456,35 +3460,35 @@
       <c r="E14" s="32"/>
       <c r="F14" s="32"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="32">
         <v>11</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="D15" s="32">
         <v>3.3</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="F15" s="32" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="32">
         <v>12</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="D16" s="32">
         <v>3.3</v>
@@ -3492,15 +3496,15 @@
       <c r="E16" s="32"/>
       <c r="F16" s="32"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="32">
         <v>13</v>
       </c>
       <c r="B17" s="32" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="D17" s="32">
         <v>3.3</v>
@@ -3508,14 +3512,14 @@
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B18" s="40" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="C18" s="41"/>
       <c r="D18" s="42"/>
       <c r="E18" s="32" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="F18" s="32"/>
     </row>

--- a/Data-file.xlsx
+++ b/Data-file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="551" documentId="8_{3CAE69A3-AE5B-4257-93BE-F3BFAEF5261B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D82F54B7-FE99-4925-89B3-E2A1C7CFFBB6}"/>
+  <xr:revisionPtr revIDLastSave="558" documentId="8_{3CAE69A3-AE5B-4257-93BE-F3BFAEF5261B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7407EFB6-B7B3-40B1-85A6-D35EDEEAA72F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{8A8E2015-1165-48D9-8246-BE8999149D44}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8A8E2015-1165-48D9-8246-BE8999149D44}"/>
   </bookViews>
   <sheets>
     <sheet name="ACC 3" sheetId="1" r:id="rId1"/>
@@ -1697,10 +1697,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2149,11 +2145,11 @@
         <v>297</v>
       </c>
       <c r="C9" s="30">
-        <v>657</v>
+        <v>736</v>
       </c>
       <c r="D9" s="31">
         <f>D8+C9</f>
-        <v>5272</v>
+        <v>5351</v>
       </c>
     </row>
   </sheetData>
@@ -2457,11 +2453,11 @@
         <v>1200</v>
       </c>
       <c r="C2" s="11">
-        <v>706</v>
+        <v>792</v>
       </c>
       <c r="D2" s="11">
         <f>B2-C2</f>
-        <v>494</v>
+        <v>408</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2472,11 +2468,11 @@
         <v>400</v>
       </c>
       <c r="C3" s="11">
-        <v>271</v>
+        <v>227</v>
       </c>
       <c r="D3" s="11">
         <f t="shared" ref="D3:D8" si="0">B3-C3</f>
-        <v>129</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2487,11 +2483,11 @@
         <v>400</v>
       </c>
       <c r="C4" s="12">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="D4" s="11">
         <f t="shared" si="0"/>
-        <v>134</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2517,11 +2513,11 @@
         <v>250</v>
       </c>
       <c r="C6" s="12">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="D6" s="11">
         <f t="shared" si="0"/>
-        <v>70</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2532,11 +2528,11 @@
         <v>100</v>
       </c>
       <c r="C7" s="12">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D7" s="11">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2547,11 +2543,11 @@
         <v>100</v>
       </c>
       <c r="C8" s="12">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D8" s="11">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2564,11 +2560,11 @@
       </c>
       <c r="C9" s="12">
         <f>SUM(C2:C8)</f>
-        <v>1885</v>
+        <v>1921</v>
       </c>
       <c r="D9" s="12">
         <f>SUM(D2:D8)</f>
-        <v>965</v>
+        <v>929</v>
       </c>
     </row>
   </sheetData>

--- a/Data-file.xlsx
+++ b/Data-file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="558" documentId="8_{3CAE69A3-AE5B-4257-93BE-F3BFAEF5261B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7407EFB6-B7B3-40B1-85A6-D35EDEEAA72F}"/>
+  <xr:revisionPtr revIDLastSave="704" documentId="8_{3CAE69A3-AE5B-4257-93BE-F3BFAEF5261B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1FD538B-7902-4303-BFEE-20D96DF12BDB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8A8E2015-1165-48D9-8246-BE8999149D44}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{8A8E2015-1165-48D9-8246-BE8999149D44}"/>
   </bookViews>
   <sheets>
     <sheet name="ACC 3" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="250">
   <si>
     <t>Month </t>
   </si>
@@ -732,6 +732,81 @@
   </si>
   <si>
     <t>10.10.26/15.10.26/31.10.26/20.11.26</t>
+  </si>
+  <si>
+    <t>GT</t>
+  </si>
+  <si>
+    <t>3 nos</t>
+  </si>
+  <si>
+    <t>UAT</t>
+  </si>
+  <si>
+    <t>2 nos</t>
+  </si>
+  <si>
+    <t>UT</t>
+  </si>
+  <si>
+    <t>AHP MCC3</t>
+  </si>
+  <si>
+    <t>ACC Fans</t>
+  </si>
+  <si>
+    <t>72 nos</t>
+  </si>
+  <si>
+    <t>Scanner air fans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seal air fans </t>
+  </si>
+  <si>
+    <t>APH</t>
+  </si>
+  <si>
+    <t>ESP Fields</t>
+  </si>
+  <si>
+    <t>120 nos</t>
+  </si>
+  <si>
+    <t>ST</t>
+  </si>
+  <si>
+    <t>1 no</t>
+  </si>
+  <si>
+    <t>ESP CR transformer</t>
+  </si>
+  <si>
+    <t>ACC transformer</t>
+  </si>
+  <si>
+    <t>10 nos</t>
+  </si>
+  <si>
+    <t>11 nos</t>
+  </si>
+  <si>
+    <t>Erected</t>
+  </si>
+  <si>
+    <t>Commissioned</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Foundation completed</t>
+  </si>
+  <si>
+    <t>11.10.26</t>
+  </si>
+  <si>
+    <t>30.09.26/10.10.26/30.10.26</t>
   </si>
 </sst>
 </file>
@@ -906,7 +981,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -1230,6 +1305,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC0D0E0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC0D0E0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1237,7 +1323,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1344,6 +1430,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1353,10 +1449,6 @@
     <xf numFmtId="0" fontId="14" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3210,325 +3302,778 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{742D201E-24F7-4C61-8302-831552FAC820}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="42" t="s">
         <v>164</v>
       </c>
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="42" t="s">
         <v>165</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="C1" s="42" t="s">
+        <v>246</v>
+      </c>
+      <c r="D1" s="42" t="s">
         <v>166</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="E1" s="42" t="s">
         <v>167</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="F1" s="42" t="s">
         <v>168</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="G1" s="42" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="44"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="44"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H1" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="I1" s="42" t="s">
+        <v>244</v>
+      </c>
+      <c r="J1" s="42" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="43"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="43"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="32">
         <v>1</v>
       </c>
       <c r="B4" s="32" t="s">
         <v>170</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="32">
+        <v>1</v>
+      </c>
+      <c r="D4" s="32" t="s">
         <v>171</v>
       </c>
-      <c r="D4" s="32">
+      <c r="E4" s="32">
         <v>11</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="F4" s="32" t="s">
         <v>172</v>
       </c>
-      <c r="F4" s="32" t="s">
+      <c r="G4" s="32" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H4" s="41">
+        <v>1</v>
+      </c>
+      <c r="I4" s="41">
+        <v>1</v>
+      </c>
+      <c r="J4" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="32">
         <v>2</v>
       </c>
       <c r="B5" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="32">
+        <v>2</v>
+      </c>
+      <c r="D5" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="32">
+      <c r="E5" s="32">
         <v>11</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="F5" s="32" t="s">
         <v>218</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="G5" s="32" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H5" s="41">
+        <v>2</v>
+      </c>
+      <c r="I5" s="41">
+        <v>2</v>
+      </c>
+      <c r="J5" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="32">
         <v>3</v>
       </c>
       <c r="B6" s="32" t="s">
         <v>176</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="32">
+        <v>2</v>
+      </c>
+      <c r="D6" s="32" t="s">
         <v>177</v>
       </c>
-      <c r="D6" s="32">
+      <c r="E6" s="32">
         <v>11</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="F6" s="32" t="s">
         <v>218</v>
       </c>
-      <c r="F6" s="32" t="s">
+      <c r="G6" s="32" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H6" s="41">
+        <v>1</v>
+      </c>
+      <c r="I6" s="41">
+        <v>1</v>
+      </c>
+      <c r="J6" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="32">
         <v>4</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="32">
+        <v>2</v>
+      </c>
+      <c r="D7" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="D7" s="32">
+      <c r="E7" s="32">
         <v>11</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="F7" s="32" t="s">
         <v>218</v>
       </c>
-      <c r="F7" s="32" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" s="32" t="s">
+        <v>249</v>
+      </c>
+      <c r="H7" s="41">
+        <v>2</v>
+      </c>
+      <c r="I7" s="41">
+        <v>1</v>
+      </c>
+      <c r="J7" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="32">
         <v>5</v>
       </c>
       <c r="B8" s="32" t="s">
         <v>181</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="32">
+        <v>3</v>
+      </c>
+      <c r="D8" s="32" t="s">
         <v>182</v>
       </c>
-      <c r="D8" s="32">
+      <c r="E8" s="32">
         <v>11</v>
       </c>
-      <c r="E8" s="32"/>
       <c r="F8" s="32"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" s="32"/>
+      <c r="H8" s="41">
+        <v>3</v>
+      </c>
+      <c r="I8" s="41">
+        <v>0</v>
+      </c>
+      <c r="J8" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="32"/>
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="44" t="s">
         <v>183</v>
       </c>
-      <c r="C9" s="41"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="32" t="s">
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="32" t="s">
         <v>184</v>
       </c>
-      <c r="F9" s="32"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" s="32"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="41"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="32">
         <v>6</v>
       </c>
       <c r="B10" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="32">
+        <v>9</v>
+      </c>
+      <c r="D10" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="D10" s="32">
+      <c r="E10" s="32">
         <v>3.3</v>
       </c>
-      <c r="E10" s="32"/>
       <c r="F10" s="32"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" s="32"/>
+      <c r="H10" s="41">
+        <v>9</v>
+      </c>
+      <c r="I10" s="41">
+        <v>9</v>
+      </c>
+      <c r="J10" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="32">
         <v>7</v>
       </c>
       <c r="B11" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="32">
+        <v>1</v>
+      </c>
+      <c r="D11" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="D11" s="32">
+      <c r="E11" s="32">
         <v>3.3</v>
       </c>
-      <c r="E11" s="32" t="s">
+      <c r="F11" s="32" t="s">
         <v>220</v>
       </c>
-      <c r="F11" s="32" t="s">
+      <c r="G11" s="32" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H11" s="41">
+        <v>9</v>
+      </c>
+      <c r="I11" s="41">
+        <v>9</v>
+      </c>
+      <c r="J11" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="32">
         <v>8</v>
       </c>
       <c r="B12" s="32" t="s">
         <v>189</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="32">
+        <v>3</v>
+      </c>
+      <c r="D12" s="32" t="s">
         <v>190</v>
       </c>
-      <c r="D12" s="32">
+      <c r="E12" s="32">
         <v>3.3</v>
       </c>
-      <c r="E12" s="32" t="s">
+      <c r="F12" s="32" t="s">
         <v>219</v>
       </c>
-      <c r="F12" s="32" t="s">
+      <c r="G12" s="32" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H12" s="41">
+        <v>3</v>
+      </c>
+      <c r="I12" s="41">
+        <v>3</v>
+      </c>
+      <c r="J12" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="32">
         <v>9</v>
       </c>
       <c r="B13" s="32" t="s">
         <v>191</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="32">
+        <v>3</v>
+      </c>
+      <c r="D13" s="32" t="s">
         <v>192</v>
       </c>
-      <c r="D13" s="32">
+      <c r="E13" s="32">
         <v>3.3</v>
       </c>
-      <c r="E13" s="32" t="s">
+      <c r="F13" s="32" t="s">
         <v>193</v>
       </c>
-      <c r="F13" s="32" t="s">
+      <c r="G13" s="32" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H13" s="41">
+        <v>3</v>
+      </c>
+      <c r="I13" s="41">
+        <v>3</v>
+      </c>
+      <c r="J13" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="32">
         <v>10</v>
       </c>
       <c r="B14" s="32" t="s">
         <v>194</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="32">
+        <v>2</v>
+      </c>
+      <c r="D14" s="32" t="s">
         <v>195</v>
       </c>
-      <c r="D14" s="32">
+      <c r="E14" s="32">
         <v>3.3</v>
       </c>
-      <c r="E14" s="32"/>
       <c r="F14" s="32"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" s="32"/>
+      <c r="H14" s="41">
+        <v>2</v>
+      </c>
+      <c r="I14" s="41">
+        <v>2</v>
+      </c>
+      <c r="J14" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="32">
         <v>11</v>
       </c>
       <c r="B15" s="32" t="s">
         <v>196</v>
       </c>
-      <c r="C15" s="32" t="s">
+      <c r="C15" s="32">
+        <v>2</v>
+      </c>
+      <c r="D15" s="32" t="s">
         <v>197</v>
       </c>
-      <c r="D15" s="32">
+      <c r="E15" s="32">
         <v>3.3</v>
       </c>
-      <c r="E15" s="32" t="s">
+      <c r="F15" s="32" t="s">
         <v>219</v>
       </c>
-      <c r="F15" s="32" t="s">
+      <c r="G15" s="32" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H15" s="41">
+        <v>2</v>
+      </c>
+      <c r="I15" s="41">
+        <v>2</v>
+      </c>
+      <c r="J15" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="32">
         <v>12</v>
       </c>
       <c r="B16" s="32" t="s">
         <v>198</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="32">
+        <v>2</v>
+      </c>
+      <c r="D16" s="32" t="s">
         <v>199</v>
       </c>
-      <c r="D16" s="32">
+      <c r="E16" s="32">
         <v>3.3</v>
       </c>
-      <c r="E16" s="32"/>
       <c r="F16" s="32"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" s="32"/>
+      <c r="H16" s="41">
+        <v>2</v>
+      </c>
+      <c r="I16" s="41">
+        <v>0</v>
+      </c>
+      <c r="J16" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="32">
         <v>13</v>
       </c>
       <c r="B17" s="32" t="s">
         <v>200</v>
       </c>
-      <c r="C17" s="32" t="s">
+      <c r="C17" s="32">
+        <v>2</v>
+      </c>
+      <c r="D17" s="32" t="s">
         <v>201</v>
       </c>
-      <c r="D17" s="32">
+      <c r="E17" s="32">
         <v>3.3</v>
       </c>
-      <c r="E17" s="32"/>
       <c r="F17" s="32"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="40" t="s">
+      <c r="G17" s="32"/>
+      <c r="H17" s="41">
+        <v>2</v>
+      </c>
+      <c r="I17" s="41">
+        <v>2</v>
+      </c>
+      <c r="J17" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="32"/>
+      <c r="B18" s="32" t="s">
         <v>202</v>
       </c>
-      <c r="C18" s="41"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="32" t="s">
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32" t="s">
         <v>203</v>
       </c>
-      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="32"/>
+      <c r="B19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="41"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="32">
+        <v>14</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>226</v>
+      </c>
+      <c r="G20" s="32"/>
+      <c r="H20" s="41">
+        <v>0</v>
+      </c>
+      <c r="I20" s="41">
+        <v>0</v>
+      </c>
+      <c r="J20" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="32">
+        <v>15</v>
+      </c>
+      <c r="B21" s="32" t="s">
+        <v>227</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="G21" s="32"/>
+      <c r="H21" s="41">
+        <v>1</v>
+      </c>
+      <c r="I21" s="41">
+        <v>1</v>
+      </c>
+      <c r="J21" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="32">
+        <v>16</v>
+      </c>
+      <c r="B22" s="32" t="s">
+        <v>229</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="G22" s="32"/>
+      <c r="H22" s="41">
+        <v>0</v>
+      </c>
+      <c r="I22" s="41">
+        <v>0</v>
+      </c>
+      <c r="J22" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="32">
+        <v>17</v>
+      </c>
+      <c r="B23" s="32" t="s">
+        <v>238</v>
+      </c>
+      <c r="C23" s="32" t="s">
+        <v>239</v>
+      </c>
+      <c r="G23" s="32" t="s">
+        <v>248</v>
+      </c>
+      <c r="H23" s="41">
+        <v>1</v>
+      </c>
+      <c r="I23" s="41">
+        <v>1</v>
+      </c>
+      <c r="J23" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="32">
+        <v>18</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>230</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="G24" s="32"/>
+      <c r="H24" s="41">
+        <v>0</v>
+      </c>
+      <c r="I24" s="41">
+        <v>0</v>
+      </c>
+      <c r="J24" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="32">
+        <v>19</v>
+      </c>
+      <c r="B25" s="32" t="s">
+        <v>231</v>
+      </c>
+      <c r="C25" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32">
+        <v>72</v>
+      </c>
+      <c r="I25" s="32">
+        <v>27</v>
+      </c>
+      <c r="J25" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="32">
+        <v>20</v>
+      </c>
+      <c r="B26" s="32" t="s">
+        <v>233</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32">
+        <v>2</v>
+      </c>
+      <c r="I26" s="32">
+        <v>2</v>
+      </c>
+      <c r="J26" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="32">
+        <v>21</v>
+      </c>
+      <c r="B27" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="C27" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32">
+        <v>2</v>
+      </c>
+      <c r="I27" s="32">
+        <v>2</v>
+      </c>
+      <c r="J27" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="32">
+        <v>22</v>
+      </c>
+      <c r="B28" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="C28" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32">
+        <v>2</v>
+      </c>
+      <c r="I28" s="32">
+        <v>1</v>
+      </c>
+      <c r="J28" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="32">
+        <v>23</v>
+      </c>
+      <c r="B29" s="32" t="s">
+        <v>236</v>
+      </c>
+      <c r="C29" s="32" t="s">
+        <v>237</v>
+      </c>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32">
+        <v>120</v>
+      </c>
+      <c r="I29" s="32">
+        <v>120</v>
+      </c>
+      <c r="J29" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="32">
+        <v>24</v>
+      </c>
+      <c r="B30" s="40" t="s">
+        <v>240</v>
+      </c>
+      <c r="C30" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32">
+        <v>0</v>
+      </c>
+      <c r="I30" s="32">
+        <v>0</v>
+      </c>
+      <c r="J30" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="32">
+        <v>25</v>
+      </c>
+      <c r="B31" s="40" t="s">
+        <v>241</v>
+      </c>
+      <c r="C31" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32">
+        <v>10</v>
+      </c>
+      <c r="I31" s="32">
+        <v>4</v>
+      </c>
+      <c r="J31" s="32">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="F1:F3"/>
-    <mergeCell ref="E1:E3"/>
+  <mergeCells count="11">
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:B3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="I1:I3"/>
+    <mergeCell ref="J1:J3"/>
     <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="H1:H3"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="G1:G3"/>
+    <mergeCell ref="F1:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data-file.xlsx
+++ b/Data-file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="704" documentId="8_{3CAE69A3-AE5B-4257-93BE-F3BFAEF5261B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1FD538B-7902-4303-BFEE-20D96DF12BDB}"/>
+  <xr:revisionPtr revIDLastSave="707" documentId="8_{3CAE69A3-AE5B-4257-93BE-F3BFAEF5261B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEB94A46-EDCE-4038-BA31-AB7FA3D7D992}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{8A8E2015-1165-48D9-8246-BE8999149D44}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="249">
   <si>
     <t>Month </t>
   </si>
@@ -726,9 +726,6 @@
   </si>
   <si>
     <t>10.10.26/15.10.26/25.10.26/10.11.26</t>
-  </si>
-  <si>
-    <t>15.09.26/25.09.26/05.10.26/15.10.26</t>
   </si>
   <si>
     <t>10.10.26/15.10.26/31.10.26/20.11.26</t>
@@ -3323,7 +3320,7 @@
         <v>165</v>
       </c>
       <c r="C1" s="42" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D1" s="42" t="s">
         <v>166</v>
@@ -3338,13 +3335,13 @@
         <v>169</v>
       </c>
       <c r="H1" s="42" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I1" s="42" t="s">
+        <v>243</v>
+      </c>
+      <c r="J1" s="42" t="s">
         <v>244</v>
-      </c>
-      <c r="J1" s="42" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -3487,7 +3484,7 @@
         <v>218</v>
       </c>
       <c r="G7" s="32" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H7" s="41">
         <v>2</v>
@@ -3594,10 +3591,10 @@
         <v>221</v>
       </c>
       <c r="H11" s="41">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I11" s="41">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J11" s="41">
         <v>0</v>
@@ -3654,9 +3651,7 @@
       <c r="F13" s="32" t="s">
         <v>193</v>
       </c>
-      <c r="G13" s="32" t="s">
-        <v>223</v>
-      </c>
+      <c r="G13" s="32"/>
       <c r="H13" s="41">
         <v>3</v>
       </c>
@@ -3715,7 +3710,7 @@
         <v>219</v>
       </c>
       <c r="G15" s="32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H15" s="41">
         <v>2</v>
@@ -3812,10 +3807,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="32" t="s">
+        <v>224</v>
+      </c>
+      <c r="C20" s="32" t="s">
         <v>225</v>
-      </c>
-      <c r="C20" s="32" t="s">
-        <v>226</v>
       </c>
       <c r="G20" s="32"/>
       <c r="H20" s="41">
@@ -3833,10 +3828,10 @@
         <v>15</v>
       </c>
       <c r="B21" s="32" t="s">
+        <v>226</v>
+      </c>
+      <c r="C21" s="32" t="s">
         <v>227</v>
-      </c>
-      <c r="C21" s="32" t="s">
-        <v>228</v>
       </c>
       <c r="G21" s="32"/>
       <c r="H21" s="41">
@@ -3854,10 +3849,10 @@
         <v>16</v>
       </c>
       <c r="B22" s="32" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C22" s="32" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G22" s="32"/>
       <c r="H22" s="41">
@@ -3875,13 +3870,13 @@
         <v>17</v>
       </c>
       <c r="B23" s="32" t="s">
+        <v>237</v>
+      </c>
+      <c r="C23" s="32" t="s">
         <v>238</v>
       </c>
-      <c r="C23" s="32" t="s">
-        <v>239</v>
-      </c>
       <c r="G23" s="32" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H23" s="41">
         <v>1</v>
@@ -3898,10 +3893,10 @@
         <v>18</v>
       </c>
       <c r="B24" s="32" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C24" s="32" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G24" s="32"/>
       <c r="H24" s="41">
@@ -3919,10 +3914,10 @@
         <v>19</v>
       </c>
       <c r="B25" s="32" t="s">
+        <v>230</v>
+      </c>
+      <c r="C25" s="32" t="s">
         <v>231</v>
-      </c>
-      <c r="C25" s="32" t="s">
-        <v>232</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32">
@@ -3940,10 +3935,10 @@
         <v>20</v>
       </c>
       <c r="B26" s="32" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C26" s="32" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32">
@@ -3961,10 +3956,10 @@
         <v>21</v>
       </c>
       <c r="B27" s="32" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C27" s="32" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G27" s="32"/>
       <c r="H27" s="32">
@@ -3982,10 +3977,10 @@
         <v>22</v>
       </c>
       <c r="B28" s="32" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C28" s="32" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G28" s="32"/>
       <c r="H28" s="32">
@@ -4003,10 +3998,10 @@
         <v>23</v>
       </c>
       <c r="B29" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="C29" s="32" t="s">
         <v>236</v>
-      </c>
-      <c r="C29" s="32" t="s">
-        <v>237</v>
       </c>
       <c r="G29" s="32"/>
       <c r="H29" s="32">
@@ -4024,10 +4019,10 @@
         <v>24</v>
       </c>
       <c r="B30" s="40" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C30" s="32" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G30" s="32"/>
       <c r="H30" s="32">
@@ -4045,10 +4040,10 @@
         <v>25</v>
       </c>
       <c r="B31" s="40" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C31" s="32" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G31" s="32"/>
       <c r="H31" s="32">

--- a/Data-file.xlsx
+++ b/Data-file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="707" documentId="8_{3CAE69A3-AE5B-4257-93BE-F3BFAEF5261B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEB94A46-EDCE-4038-BA31-AB7FA3D7D992}"/>
+  <xr:revisionPtr revIDLastSave="734" documentId="8_{3CAE69A3-AE5B-4257-93BE-F3BFAEF5261B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD892B39-3F3C-4814-AA1C-C6FF70944952}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{8A8E2015-1165-48D9-8246-BE8999149D44}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="7" xr2:uid="{8A8E2015-1165-48D9-8246-BE8999149D44}"/>
   </bookViews>
   <sheets>
     <sheet name="ACC 3" sheetId="1" r:id="rId1"/>
@@ -60,25 +60,28 @@
     <t>Cumulative erection</t>
   </si>
   <si>
-    <t>Mar’25</t>
-  </si>
-  <si>
-    <t>Apr’25</t>
-  </si>
-  <si>
-    <t>May’25</t>
-  </si>
-  <si>
-    <t>Jun’25</t>
-  </si>
-  <si>
-    <t>Jul'25</t>
-  </si>
-  <si>
-    <t>Aug'25</t>
-  </si>
-  <si>
-    <t>Sep'25</t>
+    <t>Mar’26</t>
+  </si>
+  <si>
+    <t>Apr’26</t>
+  </si>
+  <si>
+    <t>May’26</t>
+  </si>
+  <si>
+    <t>Jun’26</t>
+  </si>
+  <si>
+    <t>Jul'26</t>
+  </si>
+  <si>
+    <t>Aug'26</t>
+  </si>
+  <si>
+    <t>Sep'26</t>
+  </si>
+  <si>
+    <t>Oct'26</t>
   </si>
   <si>
     <t xml:space="preserve">Milestone </t>
@@ -108,13 +111,25 @@
     <t>TG Oil Flushing completion</t>
   </si>
   <si>
+    <t>31.10.26/25.11.26/10.12.27</t>
+  </si>
+  <si>
     <t>Boiler Light up</t>
   </si>
   <si>
+    <t>25.10.26/05.12.26/25.12.27</t>
+  </si>
+  <si>
     <t xml:space="preserve">Steam Blowing Completion </t>
   </si>
   <si>
+    <t>30.11.26/31.12.26/15.01.27</t>
+  </si>
+  <si>
     <t>Sync</t>
+  </si>
+  <si>
+    <t>25.01.27/31.01.27/26.02.27</t>
   </si>
   <si>
     <t>Full Load</t>
@@ -152,12 +167,27 @@
     <t>RHS CER to ESP </t>
   </si>
   <si>
+    <t>10 / 12 Foundations </t>
+  </si>
+  <si>
+    <t>FD/ID/PA 3B cable route-30.06.26/15.07.26/30.07.26/10.08.26/31.08.26/10.09.26/20.09.26/30.09.26/25.10.26</t>
+  </si>
+  <si>
     <t>LHS CER to ESP </t>
   </si>
   <si>
+    <t>5 / 7 Foundations </t>
+  </si>
+  <si>
+    <t>ID3A cable route-30.06.26/15.07.26/30.07.26/14.08.26/05.09.26/20.09.26/30.09.26/20.10.26 (last one after centre section removal)</t>
+  </si>
+  <si>
     <t>CER to Boiler </t>
   </si>
   <si>
+    <t>Completed</t>
+  </si>
+  <si>
     <t>FD3A/PA3A cable route-30.06.26/15.07.26/30.07.26/14.08.26/05.09.26/20.09.26</t>
   </si>
   <si>
@@ -167,6 +197,9 @@
     <t>3/8 Foundations </t>
   </si>
   <si>
+    <t>ESP CR to ESP cablings-30.07.26/20.08.26/10.09.26/15.09.26/30.09.26/31.10.26</t>
+  </si>
+  <si>
     <t>ESP to ESP Control Room (RHS) - RVPR</t>
   </si>
   <si>
@@ -176,6 +209,12 @@
     <t>FD-3A</t>
   </si>
   <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 30.08.26/30.09.26/15.10.26/30.10.26</t>
+  </si>
+  <si>
     <t>PA 3A</t>
   </si>
   <si>
@@ -191,9 +230,6 @@
     <t>BA Hopper foundation</t>
   </si>
   <si>
-    <t>Completed</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
@@ -206,6 +242,9 @@
     <t>RE</t>
   </si>
   <si>
+    <t>Capex till Sep end</t>
+  </si>
+  <si>
     <t xml:space="preserve">Agency </t>
   </si>
   <si>
@@ -557,6 +596,9 @@
     <t>MOTOR ID</t>
   </si>
   <si>
+    <t>Total</t>
+  </si>
+  <si>
     <t>NAME PLATE RATING</t>
   </si>
   <si>
@@ -569,6 +611,15 @@
     <t>Motor trial dates</t>
   </si>
   <si>
+    <t>Foundation completed</t>
+  </si>
+  <si>
+    <t>Erected</t>
+  </si>
+  <si>
+    <t>Commissioned</t>
+  </si>
+  <si>
     <t>MDBFP</t>
   </si>
   <si>
@@ -578,30 +629,30 @@
     <t>Charged</t>
   </si>
   <si>
-    <t>25.10.26 (Readiness for trial)</t>
-  </si>
-  <si>
     <t>ID FAN</t>
   </si>
   <si>
     <t>14425 KW</t>
   </si>
   <si>
+    <t>25.10.26/30.11.26</t>
+  </si>
+  <si>
     <t>FD FAN</t>
   </si>
   <si>
     <t>2800 KW</t>
   </si>
   <si>
-    <t>30.09.26/10.10.26/25.10.26</t>
-  </si>
-  <si>
     <t>PA FAN</t>
   </si>
   <si>
     <t>4825 KW</t>
   </si>
   <si>
+    <t>30.09.26/10.10.26/30.10.26</t>
+  </si>
+  <si>
     <t>CEP</t>
   </si>
   <si>
@@ -626,12 +677,24 @@
     <t>930 KW</t>
   </si>
   <si>
+    <t>25.09.26/10.10.26/20.10.26/04.11.26</t>
+  </si>
+  <si>
+    <t>05.10.26/20.10.26/25.10.26/20.11.26</t>
+  </si>
+  <si>
     <t>ECW PUMP (TG)</t>
   </si>
   <si>
     <t>200 KW</t>
   </si>
   <si>
+    <t>10.10.26/20.10.26/04.11.26</t>
+  </si>
+  <si>
+    <t>10.10.26/15.10.26/25.10.26/10.11.26</t>
+  </si>
+  <si>
     <t>ACW PUMP</t>
   </si>
   <si>
@@ -653,6 +716,9 @@
     <t>160 KW</t>
   </si>
   <si>
+    <t>10.10.26/15.10.26/31.10.26/20.11.26</t>
+  </si>
+  <si>
     <t>DRIP PUMP</t>
   </si>
   <si>
@@ -671,66 +737,6 @@
     <t>0/24 motor trial done till date</t>
   </si>
   <si>
-    <t>Oct'25</t>
-  </si>
-  <si>
-    <t>25.10.26/05.12.26/25.12.27</t>
-  </si>
-  <si>
-    <t>30.11.26/31.12.26/15.01.27</t>
-  </si>
-  <si>
-    <t>25.01.27/31.01.27/26.02.27</t>
-  </si>
-  <si>
-    <t>31.10.26/25.11.26/10.12.27</t>
-  </si>
-  <si>
-    <t>Capex till Sep end</t>
-  </si>
-  <si>
-    <t>25.10.26/30.11.26</t>
-  </si>
-  <si>
-    <t>In Progress</t>
-  </si>
-  <si>
-    <t>10 / 12 Foundations </t>
-  </si>
-  <si>
-    <t>5 / 7 Foundations </t>
-  </si>
-  <si>
-    <t>FD/ID/PA 3B cable route-30.06.26/15.07.26/30.07.26/10.08.26/31.08.26/10.09.26/20.09.26/30.09.26/25.10.26</t>
-  </si>
-  <si>
-    <t>ID3A cable route-30.06.26/15.07.26/30.07.26/14.08.26/05.09.26/20.09.26/30.09.26/20.10.26 (last one after centre section removal)</t>
-  </si>
-  <si>
-    <t>ESP CR to ESP cablings-30.07.26/20.08.26/10.09.26/15.09.26/30.09.26/31.10.26</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 30.08.26/30.09.26/15.10.26/30.10.26</t>
-  </si>
-  <si>
-    <t>15.10.26/25.10.26</t>
-  </si>
-  <si>
-    <t>10.10.26/20.10.26/04.11.26</t>
-  </si>
-  <si>
-    <t>25.09.26/10.10.26/20.10.26/04.11.26</t>
-  </si>
-  <si>
-    <t>05.10.26/20.10.26/25.10.26/20.11.26</t>
-  </si>
-  <si>
-    <t>10.10.26/15.10.26/25.10.26/10.11.26</t>
-  </si>
-  <si>
-    <t>10.10.26/15.10.26/31.10.26/20.11.26</t>
-  </si>
-  <si>
     <t>GT</t>
   </si>
   <si>
@@ -746,6 +752,15 @@
     <t>UT</t>
   </si>
   <si>
+    <t>ST</t>
+  </si>
+  <si>
+    <t>1 no</t>
+  </si>
+  <si>
+    <t>11.10.26</t>
+  </si>
+  <si>
     <t>AHP MCC3</t>
   </si>
   <si>
@@ -770,47 +785,32 @@
     <t>120 nos</t>
   </si>
   <si>
-    <t>ST</t>
-  </si>
-  <si>
-    <t>1 no</t>
-  </si>
-  <si>
     <t>ESP CR transformer</t>
   </si>
   <si>
+    <t>10 nos</t>
+  </si>
+  <si>
     <t>ACC transformer</t>
   </si>
   <si>
-    <t>10 nos</t>
-  </si>
-  <si>
     <t>11 nos</t>
   </si>
   <si>
-    <t>Erected</t>
-  </si>
-  <si>
-    <t>Commissioned</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Foundation completed</t>
-  </si>
-  <si>
-    <t>11.10.26</t>
-  </si>
-  <si>
-    <t>30.09.26/10.10.26/30.10.26</t>
+    <t>31.10.26 (Readiness for trial)</t>
+  </si>
+  <si>
+    <t>30.09.26/10.10.26/25.10.26/31.10.26</t>
+  </si>
+  <si>
+    <t>B board charged</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -928,6 +928,12 @@
       <sz val="12"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1786,6 +1792,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2104,14 +2114,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{862506E9-25B6-4CBA-A38B-FADA62B5D706}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2125,7 +2135,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
@@ -2139,7 +2149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A3" s="14" t="s">
         <v>5</v>
       </c>
@@ -2153,7 +2163,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A4" s="16" t="s">
         <v>6</v>
       </c>
@@ -2167,7 +2177,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A5" s="30" t="s">
         <v>7</v>
       </c>
@@ -2181,7 +2191,7 @@
         <v>1815</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A6" s="30" t="s">
         <v>8</v>
       </c>
@@ -2196,7 +2206,7 @@
         <v>2688</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A7" s="30" t="s">
         <v>9</v>
       </c>
@@ -2211,7 +2221,7 @@
         <v>3493</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A8" s="30" t="s">
         <v>10</v>
       </c>
@@ -2226,22 +2236,23 @@
         <v>4615</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A9" s="30" t="s">
-        <v>204</v>
+        <v>11</v>
       </c>
       <c r="B9" s="30">
         <v>297</v>
       </c>
       <c r="C9" s="30">
-        <v>736</v>
+        <v>931</v>
       </c>
       <c r="D9" s="31">
         <f>D8+C9</f>
-        <v>5351</v>
+        <v>5546</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2249,90 +2260,90 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9917535D-21FB-4B58-A8DD-F27CB281E1B3}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.73046875" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A3" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="30.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="30.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="7" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -2343,118 +2354,118 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F89D7ACF-216A-4C43-82E3-F1E9ECF11B39}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="24.5703125" customWidth="1"/>
+    <col min="1" max="1" width="24.59765625" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" customWidth="1"/>
+    <col min="3" max="3" width="41.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="31.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="19" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="47.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" s="23" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>212</v>
+        <v>36</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="63.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A3" s="23" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>213</v>
+        <v>39</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="47.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="23" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B4" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="47.25" x14ac:dyDescent="0.45">
+      <c r="A5" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="24" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
-        <v>34</v>
-      </c>
       <c r="B5" s="26" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A6" s="28" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A7" s="28" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>211</v>
+        <v>50</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A8" s="28" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A9" s="28" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C9" s="28" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A10" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="28" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="28" t="s">
-        <v>44</v>
       </c>
       <c r="C10" s="29"/>
     </row>
@@ -2466,25 +2477,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73E19115-1CD0-4934-BDF4-4937A2D87F36}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B1" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B2">
         <v>1448.3</v>
@@ -2493,9 +2504,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>209</v>
+        <v>61</v>
       </c>
       <c r="B3">
         <v>573.82000000000005</v>
@@ -2513,135 +2524,135 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73BDED7B-F217-445A-9C06-91034F503C5D}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="27.7109375" customWidth="1"/>
-    <col min="2" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" customWidth="1"/>
+    <col min="1" max="1" width="27.73046875" customWidth="1"/>
+    <col min="2" max="3" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="28.15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="8" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="10" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="B2" s="11">
         <v>1200</v>
       </c>
       <c r="C2" s="11">
-        <v>792</v>
+        <v>410</v>
       </c>
       <c r="D2" s="11">
         <f>B2-C2</f>
-        <v>408</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="10" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="B3" s="11">
         <v>400</v>
       </c>
       <c r="C3" s="11">
-        <v>227</v>
+        <v>103</v>
       </c>
       <c r="D3" s="11">
         <f t="shared" ref="D3:D8" si="0">B3-C3</f>
-        <v>173</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="10" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="B4" s="12">
         <v>400</v>
       </c>
       <c r="C4" s="12">
-        <v>257</v>
+        <v>150</v>
       </c>
       <c r="D4" s="11">
         <f t="shared" si="0"/>
-        <v>143</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="10" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="B5" s="12">
         <v>400</v>
       </c>
       <c r="C5" s="12">
-        <v>301</v>
+        <v>215</v>
       </c>
       <c r="D5" s="11">
         <f t="shared" si="0"/>
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="10" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="B6" s="12">
         <v>250</v>
       </c>
       <c r="C6" s="12">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="D6" s="11">
         <f t="shared" si="0"/>
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="10" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="B7" s="12">
         <v>100</v>
       </c>
       <c r="C7" s="12">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D7" s="11">
         <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="10" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="B8" s="12">
         <v>100</v>
       </c>
       <c r="C8" s="12">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="D8" s="11">
         <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="10" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="B9" s="12">
         <f>SUM(B2:B8)</f>
@@ -2649,11 +2660,11 @@
       </c>
       <c r="C9" s="12">
         <f>SUM(C2:C8)</f>
-        <v>1921</v>
+        <v>1130</v>
       </c>
       <c r="D9" s="12">
         <f>SUM(D2:D8)</f>
-        <v>929</v>
+        <v>1720</v>
       </c>
     </row>
   </sheetData>
@@ -2664,7 +2675,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{937E703F-939A-4FE6-A55F-3284F68BDE73}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2674,622 +2685,622 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC87E3DB-D54A-4C9B-8DF9-428C70D3A6F3}">
   <dimension ref="A1:W303"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.73046875" customWidth="1"/>
+    <col min="5" max="5" width="14.73046875" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="23" max="23" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="2.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="39" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="39" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="37" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="C1" s="37" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D1" s="37" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="E1" s="37" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="F1" s="37" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="G1" s="37" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="H1" s="37" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="I1" s="39" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="J1" s="39" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="K1" s="39" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="L1" s="39" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A2" s="35" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D2" s="35" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="E2" s="35" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G2" s="35" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="H2" s="35" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A3" s="35" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="E3" s="35" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H3" s="35" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A4" s="35" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="B4" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="E4" s="35" t="s">
+        <v>102</v>
+      </c>
+      <c r="F4" s="35" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="H4" s="35" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A5" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="E5" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="F5" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="G5" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="H5" s="35" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A6" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>115</v>
+      </c>
+      <c r="F6" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="35" t="s">
-        <v>87</v>
-      </c>
-      <c r="D4" s="35" t="s">
-        <v>88</v>
-      </c>
-      <c r="E4" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="F4" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="G4" s="35" t="s">
-        <v>79</v>
-      </c>
-      <c r="H4" s="35" t="s">
+      <c r="G6" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="H6" s="35" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A7" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>119</v>
+      </c>
+      <c r="E7" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="F7" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="H7" s="35" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A8" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="G8" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="H8" s="35" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A9" s="35" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="F9" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="G9" s="35" t="s">
+        <v>98</v>
+      </c>
+      <c r="H9" s="35" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A10" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="D10" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="E10" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="F10" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="G10" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="H10" s="35" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A11" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="D11" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="E11" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="F11" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="G11" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="H11" s="38" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A12" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>137</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="F12" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="G12" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="H12" s="38" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A13" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="B13" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="C13" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="D13" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="F13" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="G13" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13" s="38" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A14" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="D14" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="E14" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="F14" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="G14" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="H14" s="35" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A15" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="D15" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="E15" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="F15" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="G15" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="H15" s="35" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A16" s="35" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="35" t="s">
+      <c r="B16" s="35" t="s">
+        <v>146</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>147</v>
+      </c>
+      <c r="D16" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="B5" s="35" t="s">
-        <v>92</v>
-      </c>
-      <c r="C5" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="D5" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="E5" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="F5" s="35" t="s">
+      <c r="F16" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="H16" s="38" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A17" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="C17" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="E17" s="38" t="s">
+        <v>152</v>
+      </c>
+      <c r="F17" s="38" t="s">
+        <v>153</v>
+      </c>
+      <c r="G17" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="H17" s="38" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A18" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>156</v>
+      </c>
+      <c r="C18" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="D18" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="E18" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="F18" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="G18" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="H18" s="35" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A19" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="B19" s="35" t="s">
+        <v>158</v>
+      </c>
+      <c r="C19" s="35" t="s">
+        <v>159</v>
+      </c>
+      <c r="D19" s="35" t="s">
+        <v>160</v>
+      </c>
+      <c r="E19" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="F19" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="G19" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="H19" s="35" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A20" s="35" t="s">
+        <v>160</v>
+      </c>
+      <c r="B20" s="35" t="s">
+        <v>161</v>
+      </c>
+      <c r="C20" s="35" t="s">
+        <v>162</v>
+      </c>
+      <c r="D20" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="G5" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="H5" s="35" t="s">
+      <c r="E20" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="F20" s="35" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="35" t="s">
-        <v>98</v>
-      </c>
-      <c r="B6" s="35" t="s">
-        <v>99</v>
-      </c>
-      <c r="C6" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="D6" s="35" t="s">
-        <v>101</v>
-      </c>
-      <c r="E6" s="35" t="s">
-        <v>102</v>
-      </c>
-      <c r="F6" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="G6" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="H6" s="35" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="B7" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="C7" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="D7" s="35" t="s">
-        <v>106</v>
-      </c>
-      <c r="E7" s="35" t="s">
-        <v>107</v>
-      </c>
-      <c r="F7" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="G7" s="35" t="s">
-        <v>107</v>
-      </c>
-      <c r="H7" s="35" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="35" t="s">
-        <v>83</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="D8" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="E8" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="F8" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="G8" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="H8" s="35" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="35" t="s">
-        <v>85</v>
-      </c>
-      <c r="B9" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="C9" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="D9" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="E9" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="F9" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="G9" s="35" t="s">
-        <v>85</v>
-      </c>
-      <c r="H9" s="35" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="B10" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="C10" s="35" t="s">
+      <c r="G20" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="H20" s="35" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A21" s="35" t="s">
         <v>119</v>
       </c>
-      <c r="D10" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="E10" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="F10" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="G10" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="H10" s="35" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="35" t="s">
-        <v>120</v>
-      </c>
-      <c r="B11" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>122</v>
-      </c>
-      <c r="D11" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="E11" s="38" t="s">
-        <v>111</v>
-      </c>
-      <c r="F11" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="G11" s="38" t="s">
-        <v>111</v>
-      </c>
-      <c r="H11" s="38" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="B12" s="35" t="s">
+      <c r="B21" s="35" t="s">
+        <v>163</v>
+      </c>
+      <c r="C21" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="D21" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="E21" s="35" t="s">
+        <v>119</v>
+      </c>
+      <c r="F21" s="35" t="s">
+        <v>165</v>
+      </c>
+      <c r="G21" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="C12" s="38" t="s">
-        <v>125</v>
-      </c>
-      <c r="D12" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="E12" s="38" t="s">
-        <v>111</v>
-      </c>
-      <c r="F12" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="G12" s="38" t="s">
-        <v>111</v>
-      </c>
-      <c r="H12" s="38" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="B13" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="D13" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="E13" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="F13" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="G13" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="H13" s="38" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="35" t="s">
-        <v>78</v>
-      </c>
-      <c r="B14" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="C14" s="35" t="s">
-        <v>129</v>
-      </c>
-      <c r="D14" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="E14" s="35" t="s">
-        <v>79</v>
-      </c>
-      <c r="F14" s="35" t="s">
-        <v>107</v>
-      </c>
-      <c r="G14" s="35" t="s">
-        <v>79</v>
-      </c>
-      <c r="H14" s="35" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="35" t="s">
-        <v>79</v>
-      </c>
-      <c r="B15" s="35" t="s">
-        <v>130</v>
-      </c>
-      <c r="C15" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="D15" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="E15" s="35" t="s">
-        <v>83</v>
-      </c>
-      <c r="F15" s="35" t="s">
-        <v>101</v>
-      </c>
-      <c r="G15" s="35" t="s">
-        <v>83</v>
-      </c>
-      <c r="H15" s="35" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="B16" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>134</v>
-      </c>
-      <c r="D16" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="E16" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="F16" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="G16" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="H16" s="38" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="35" t="s">
-        <v>116</v>
-      </c>
-      <c r="B17" s="35" t="s">
+      <c r="H21" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="C17" s="38" t="s">
-        <v>137</v>
-      </c>
-      <c r="D17" s="38" t="s">
-        <v>138</v>
-      </c>
-      <c r="E17" s="38" t="s">
-        <v>139</v>
-      </c>
-      <c r="F17" s="38" t="s">
-        <v>140</v>
-      </c>
-      <c r="G17" s="38" t="s">
-        <v>106</v>
-      </c>
-      <c r="H17" s="38" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="B18" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="C18" s="35" t="s">
-        <v>144</v>
-      </c>
-      <c r="D18" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="E18" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="F18" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="G18" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="H18" s="35" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="35" t="s">
-        <v>107</v>
-      </c>
-      <c r="B19" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="C19" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="D19" s="35" t="s">
-        <v>147</v>
-      </c>
-      <c r="E19" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="F19" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="G19" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="H19" s="35" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="35" t="s">
-        <v>147</v>
-      </c>
-      <c r="B20" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="D20" s="35" t="s">
-        <v>83</v>
-      </c>
-      <c r="E20" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="F20" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="G20" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="H20" s="35" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="35" t="s">
-        <v>106</v>
-      </c>
-      <c r="B21" s="35" t="s">
-        <v>150</v>
-      </c>
-      <c r="C21" s="35" t="s">
-        <v>151</v>
-      </c>
-      <c r="D21" s="35" t="s">
-        <v>123</v>
-      </c>
-      <c r="E21" s="35" t="s">
-        <v>106</v>
-      </c>
-      <c r="F21" s="35" t="s">
-        <v>152</v>
-      </c>
-      <c r="G21" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="H21" s="35" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A22" s="36"/>
       <c r="B22" s="36"/>
       <c r="C22" s="37" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" hidden="1" x14ac:dyDescent="0.5">
       <c r="A23" s="33"/>
       <c r="B23" s="33"/>
       <c r="C23" s="34" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="D23" s="33"/>
       <c r="E23" s="34" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="F23" s="34" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="G23" s="34" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="H23" s="34" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="303" spans="23:23" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="303" spans="23:23" x14ac:dyDescent="0.45">
       <c r="W303" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -3300,51 +3311,51 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{742D201E-24F7-4C61-8302-831552FAC820}">
   <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.86328125" customWidth="1"/>
+    <col min="4" max="4" width="17.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.73046875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.42578125" customWidth="1"/>
+    <col min="10" max="10" width="20.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="42" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="B1" s="42" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="C1" s="42" t="s">
-        <v>245</v>
+        <v>179</v>
       </c>
       <c r="D1" s="42" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="E1" s="42" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="F1" s="42" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="G1" s="42" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="H1" s="42" t="s">
-        <v>246</v>
+        <v>184</v>
       </c>
       <c r="I1" s="42" t="s">
-        <v>243</v>
+        <v>185</v>
       </c>
       <c r="J1" s="42" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="43"/>
       <c r="B2" s="43"/>
       <c r="C2" s="43"/>
@@ -3356,7 +3367,7 @@
       <c r="I2" s="43"/>
       <c r="J2" s="43"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="43"/>
       <c r="B3" s="43"/>
       <c r="C3" s="43"/>
@@ -3368,27 +3379,27 @@
       <c r="I3" s="43"/>
       <c r="J3" s="43"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="32">
         <v>1</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="C4" s="32">
         <v>1</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="E4" s="32">
         <v>11</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>173</v>
+        <v>246</v>
       </c>
       <c r="H4" s="41">
         <v>1</v>
@@ -3400,27 +3411,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="32">
         <v>2</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="C5" s="32">
         <v>2</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="E5" s="32">
         <v>11</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="G5" s="32" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="H5" s="41">
         <v>2</v>
@@ -3432,27 +3443,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="32">
         <v>3</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="C6" s="32">
         <v>2</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="E6" s="32">
         <v>11</v>
       </c>
       <c r="F6" s="32" t="s">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>178</v>
+        <v>247</v>
       </c>
       <c r="H6" s="41">
         <v>1</v>
@@ -3464,27 +3475,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="32">
         <v>4</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="C7" s="32">
         <v>2</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="E7" s="32">
         <v>11</v>
       </c>
       <c r="F7" s="32" t="s">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="G7" s="32" t="s">
-        <v>248</v>
+        <v>197</v>
       </c>
       <c r="H7" s="41">
         <v>2</v>
@@ -3496,18 +3507,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="32">
         <v>5</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="C8" s="32">
         <v>3</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="E8" s="32">
         <v>11</v>
@@ -3524,34 +3535,34 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" s="32"/>
       <c r="B9" s="44" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="C9" s="45"/>
       <c r="D9" s="45"/>
       <c r="E9" s="46"/>
       <c r="F9" s="32" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="G9" s="32"/>
       <c r="H9" s="41"/>
       <c r="I9" s="41"/>
       <c r="J9" s="41"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="32">
         <v>6</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="C10" s="32">
         <v>9</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E10" s="32">
         <v>3.3</v>
@@ -3568,27 +3579,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" s="32">
         <v>7</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="C11" s="32">
         <v>1</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="E11" s="32">
         <v>3.3</v>
       </c>
       <c r="F11" s="32" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="G11" s="32" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H11" s="41">
         <v>1</v>
@@ -3600,27 +3611,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="32">
         <v>8</v>
       </c>
       <c r="B12" s="32" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="C12" s="32">
         <v>3</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="E12" s="32">
         <v>3.3</v>
       </c>
       <c r="F12" s="32" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="G12" s="32" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="H12" s="41">
         <v>3</v>
@@ -3632,24 +3643,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" s="32">
         <v>9</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="C13" s="32">
         <v>3</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="E13" s="32">
         <v>3.3</v>
       </c>
       <c r="F13" s="32" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="G13" s="32"/>
       <c r="H13" s="41">
@@ -3662,18 +3673,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" s="32">
         <v>10</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="C14" s="32">
         <v>2</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="E14" s="32">
         <v>3.3</v>
@@ -3690,27 +3701,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" s="32">
         <v>11</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="C15" s="32">
         <v>2</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="E15" s="32">
         <v>3.3</v>
       </c>
       <c r="F15" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="G15" s="32" t="s">
         <v>219</v>
-      </c>
-      <c r="G15" s="32" t="s">
-        <v>223</v>
       </c>
       <c r="H15" s="41">
         <v>2</v>
@@ -3722,18 +3733,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" s="32">
         <v>12</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="C16" s="32">
         <v>2</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="E16" s="32">
         <v>3.3</v>
@@ -3750,18 +3761,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" s="32">
         <v>13</v>
       </c>
       <c r="B17" s="32" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="C17" s="32">
         <v>2</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="E17" s="32">
         <v>3.3</v>
@@ -3778,23 +3789,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" s="32"/>
       <c r="B18" s="32" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="C18" s="32"/>
       <c r="D18" s="32"/>
       <c r="E18" s="32"/>
       <c r="F18" s="32" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="G18" s="32"/>
       <c r="H18" s="41"/>
       <c r="I18" s="41"/>
       <c r="J18" s="41"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" s="32"/>
       <c r="B19" s="32"/>
       <c r="G19" s="32"/>
@@ -3802,15 +3813,15 @@
       <c r="I19" s="41"/>
       <c r="J19" s="41"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" s="32">
         <v>14</v>
       </c>
       <c r="B20" s="32" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C20" s="32" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G20" s="32"/>
       <c r="H20" s="41">
@@ -3823,15 +3834,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" s="32">
         <v>15</v>
       </c>
       <c r="B21" s="32" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C21" s="32" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G21" s="32"/>
       <c r="H21" s="41">
@@ -3844,15 +3855,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" s="32">
         <v>16</v>
       </c>
       <c r="B22" s="32" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C22" s="32" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G22" s="32"/>
       <c r="H22" s="41">
@@ -3865,18 +3876,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" s="32">
         <v>17</v>
       </c>
       <c r="B23" s="32" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G23" s="32" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="H23" s="41">
         <v>1</v>
@@ -3888,15 +3899,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" s="32">
         <v>18</v>
       </c>
       <c r="B24" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="C24" s="32" t="s">
         <v>229</v>
-      </c>
-      <c r="C24" s="32" t="s">
-        <v>227</v>
       </c>
       <c r="G24" s="32"/>
       <c r="H24" s="41">
@@ -3909,15 +3920,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" s="32">
         <v>19</v>
       </c>
       <c r="B25" s="32" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C25" s="32" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32">
@@ -3930,15 +3941,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" s="32">
         <v>20</v>
       </c>
       <c r="B26" s="32" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C26" s="32" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32">
@@ -3951,15 +3962,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27" s="32">
         <v>21</v>
       </c>
       <c r="B27" s="32" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C27" s="32" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G27" s="32"/>
       <c r="H27" s="32">
@@ -3972,15 +3983,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28" s="32">
         <v>22</v>
       </c>
       <c r="B28" s="32" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="C28" s="32" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G28" s="32"/>
       <c r="H28" s="32">
@@ -3993,15 +4004,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A29" s="32">
         <v>23</v>
       </c>
       <c r="B29" s="32" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C29" s="32" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="G29" s="32"/>
       <c r="H29" s="32">
@@ -4014,15 +4025,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A30" s="32">
         <v>24</v>
       </c>
       <c r="B30" s="40" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C30" s="32" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G30" s="32"/>
       <c r="H30" s="32">
@@ -4035,15 +4046,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" s="32">
         <v>25</v>
       </c>
       <c r="B31" s="40" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C31" s="32" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="G31" s="32"/>
       <c r="H31" s="32">

--- a/Data-file.xlsx
+++ b/Data-file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="734" documentId="8_{3CAE69A3-AE5B-4257-93BE-F3BFAEF5261B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD892B39-3F3C-4814-AA1C-C6FF70944952}"/>
+  <xr:revisionPtr revIDLastSave="749" documentId="8_{3CAE69A3-AE5B-4257-93BE-F3BFAEF5261B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B238CA84-64DD-4AF1-97BF-56752043C7E3}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="7" xr2:uid="{8A8E2015-1165-48D9-8246-BE8999149D44}"/>
+    <workbookView xWindow="7980" yWindow="4185" windowWidth="18045" windowHeight="11295" xr2:uid="{8A8E2015-1165-48D9-8246-BE8999149D44}"/>
   </bookViews>
   <sheets>
     <sheet name="ACC 3" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="250">
   <si>
     <t>Month </t>
   </si>
@@ -804,6 +804,9 @@
   </si>
   <si>
     <t>B board charged</t>
+  </si>
+  <si>
+    <t>M&amp;S - Piping works</t>
   </si>
 </sst>
 </file>
@@ -2114,14 +2117,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{862506E9-25B6-4CBA-A38B-FADA62B5D706}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:4" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2135,7 +2138,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
@@ -2149,7 +2152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>5</v>
       </c>
@@ -2163,7 +2166,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>6</v>
       </c>
@@ -2177,7 +2180,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="30" t="s">
         <v>7</v>
       </c>
@@ -2191,7 +2194,7 @@
         <v>1815</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="30" t="s">
         <v>8</v>
       </c>
@@ -2206,7 +2209,7 @@
         <v>2688</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="30" t="s">
         <v>9</v>
       </c>
@@ -2221,7 +2224,7 @@
         <v>3493</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="30" t="s">
         <v>10</v>
       </c>
@@ -2236,7 +2239,7 @@
         <v>4615</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="30" t="s">
         <v>11</v>
       </c>
@@ -2244,11 +2247,11 @@
         <v>297</v>
       </c>
       <c r="C9" s="30">
-        <v>931</v>
+        <v>994</v>
       </c>
       <c r="D9" s="31">
         <f>D8+C9</f>
-        <v>5546</v>
+        <v>5609</v>
       </c>
     </row>
   </sheetData>
@@ -2260,13 +2263,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9917535D-21FB-4B58-A8DD-F27CB281E1B3}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.73046875" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -2274,7 +2277,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
@@ -2282,7 +2285,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>16</v>
       </c>
@@ -2290,7 +2293,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>18</v>
       </c>
@@ -2298,7 +2301,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30.4" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>20</v>
       </c>
@@ -2306,7 +2309,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>22</v>
       </c>
@@ -2314,7 +2317,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="30.4" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>24</v>
       </c>
@@ -2322,7 +2325,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>26</v>
       </c>
@@ -2330,7 +2333,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>28</v>
       </c>
@@ -2338,7 +2341,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>30</v>
       </c>
@@ -2354,14 +2357,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F89D7ACF-216A-4C43-82E3-F1E9ECF11B39}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.59765625" customWidth="1"/>
+    <col min="1" max="1" width="24.5703125" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="41.1328125" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="31.9" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>32</v>
       </c>
@@ -2372,7 +2375,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="47.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:3" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>35</v>
       </c>
@@ -2383,7 +2386,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="63.4" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:3" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>38</v>
       </c>
@@ -2394,7 +2397,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="47.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="23" t="s">
         <v>41</v>
       </c>
@@ -2405,7 +2408,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="47.25" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
         <v>44</v>
       </c>
@@ -2416,7 +2419,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="47.25" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
         <v>47</v>
       </c>
@@ -2427,7 +2430,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
         <v>49</v>
       </c>
@@ -2438,7 +2441,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
         <v>52</v>
       </c>
@@ -2449,7 +2452,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
         <v>54</v>
       </c>
@@ -2460,7 +2463,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
         <v>56</v>
       </c>
@@ -2477,12 +2480,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73E19115-1CD0-4934-BDF4-4937A2D87F36}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>57</v>
       </c>
@@ -2493,7 +2496,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -2504,7 +2507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -2523,15 +2526,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73BDED7B-F217-445A-9C06-91034F503C5D}">
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.73046875" customWidth="1"/>
-    <col min="2" max="3" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.265625" customWidth="1"/>
+    <col min="1" max="1" width="27.7109375" customWidth="1"/>
+    <col min="2" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.15" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>62</v>
       </c>
@@ -2545,7 +2548,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>66</v>
       </c>
@@ -2553,118 +2556,133 @@
         <v>1200</v>
       </c>
       <c r="C2" s="11">
-        <v>410</v>
+        <v>741</v>
       </c>
       <c r="D2" s="11">
         <f>B2-C2</f>
-        <v>790</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>67</v>
       </c>
       <c r="B3" s="11">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="C3" s="11">
-        <v>103</v>
+        <v>207</v>
       </c>
       <c r="D3" s="11">
-        <f t="shared" ref="D3:D8" si="0">B3-C3</f>
-        <v>297</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+        <f t="shared" ref="D3:D10" si="0">B3-C3</f>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B4" s="12">
-        <v>400</v>
-      </c>
-      <c r="C4" s="12">
-        <v>150</v>
+        <v>249</v>
+      </c>
+      <c r="B4" s="11">
+        <v>200</v>
+      </c>
+      <c r="C4" s="11">
+        <v>75</v>
       </c>
       <c r="D4" s="11">
         <f t="shared" si="0"/>
-        <v>250</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B5" s="12">
         <v>400</v>
       </c>
       <c r="C5" s="12">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="D5" s="11">
         <f t="shared" si="0"/>
-        <v>185</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B6" s="12">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="C6" s="12">
-        <v>150</v>
+        <v>296</v>
       </c>
       <c r="D6" s="11">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B7" s="12">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="C7" s="12">
-        <v>70</v>
+        <v>198</v>
       </c>
       <c r="D7" s="11">
         <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B8" s="12">
         <v>100</v>
       </c>
       <c r="C8" s="12">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="D8" s="11">
         <f t="shared" si="0"/>
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="12">
+        <v>100</v>
+      </c>
+      <c r="C9" s="12">
+        <v>66</v>
+      </c>
+      <c r="D9" s="11">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B9" s="12">
-        <f>SUM(B2:B8)</f>
-        <v>2850</v>
-      </c>
-      <c r="C9" s="12">
-        <f>SUM(C2:C8)</f>
-        <v>1130</v>
-      </c>
-      <c r="D9" s="12">
-        <f>SUM(D2:D8)</f>
-        <v>1720</v>
+      <c r="B10" s="12">
+        <f>SUM(B2:B9)</f>
+        <v>2950</v>
+      </c>
+      <c r="C10" s="12">
+        <f>SUM(C2:C9)</f>
+        <v>1884</v>
+      </c>
+      <c r="D10" s="11">
+        <f t="shared" si="0"/>
+        <v>1066</v>
       </c>
     </row>
   </sheetData>
@@ -2675,7 +2693,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{937E703F-939A-4FE6-A55F-3284F68BDE73}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2685,20 +2703,20 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC87E3DB-D54A-4C9B-8DF9-428C70D3A6F3}">
   <dimension ref="A1:W303"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.73046875" customWidth="1"/>
-    <col min="5" max="5" width="14.73046875" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="23" max="23" width="2.73046875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="2.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="39" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" s="39" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="37" t="s">
         <v>74</v>
       </c>
@@ -2736,7 +2754,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
         <v>86</v>
       </c>
@@ -2762,7 +2780,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="35" t="s">
         <v>93</v>
       </c>
@@ -2788,7 +2806,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>93</v>
       </c>
@@ -2814,7 +2832,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>104</v>
       </c>
@@ -2840,7 +2858,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>111</v>
       </c>
@@ -2866,7 +2884,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>97</v>
       </c>
@@ -2892,7 +2910,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="35" t="s">
         <v>96</v>
       </c>
@@ -2918,7 +2936,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="35" t="s">
         <v>98</v>
       </c>
@@ -2944,7 +2962,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="35" t="s">
         <v>130</v>
       </c>
@@ -2970,7 +2988,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="35" t="s">
         <v>133</v>
       </c>
@@ -2996,7 +3014,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="35" t="s">
         <v>123</v>
       </c>
@@ -3022,7 +3040,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="35" t="s">
         <v>128</v>
       </c>
@@ -3048,7 +3066,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="35" t="s">
         <v>91</v>
       </c>
@@ -3074,7 +3092,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="35" t="s">
         <v>92</v>
       </c>
@@ -3100,7 +3118,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="35" t="s">
         <v>90</v>
       </c>
@@ -3126,7 +3144,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="35" t="s">
         <v>129</v>
       </c>
@@ -3152,7 +3170,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="35" t="s">
         <v>155</v>
       </c>
@@ -3178,7 +3196,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A19" s="35" t="s">
         <v>120</v>
       </c>
@@ -3204,7 +3222,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="35" t="s">
         <v>160</v>
       </c>
@@ -3230,7 +3248,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="35" t="s">
         <v>119</v>
       </c>
@@ -3256,7 +3274,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="36"/>
       <c r="B22" s="36"/>
       <c r="C22" s="37" t="s">
@@ -3278,7 +3296,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.75" hidden="1" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:8" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="33"/>
       <c r="B23" s="33"/>
       <c r="C23" s="34" t="s">
@@ -3298,7 +3316,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="303" spans="23:23" x14ac:dyDescent="0.45">
+    <row r="303" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W303" t="s">
         <v>176</v>
       </c>
@@ -3311,19 +3329,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{742D201E-24F7-4C61-8302-831552FAC820}">
   <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.86328125" customWidth="1"/>
-    <col min="4" max="4" width="17.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.3984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.3984375" customWidth="1"/>
+    <col min="10" max="10" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="42" t="s">
         <v>177</v>
       </c>
@@ -3355,7 +3373,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="43"/>
       <c r="B2" s="43"/>
       <c r="C2" s="43"/>
@@ -3367,7 +3385,7 @@
       <c r="I2" s="43"/>
       <c r="J2" s="43"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="43"/>
       <c r="B3" s="43"/>
       <c r="C3" s="43"/>
@@ -3379,7 +3397,7 @@
       <c r="I3" s="43"/>
       <c r="J3" s="43"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="32">
         <v>1</v>
       </c>
@@ -3411,7 +3429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="32">
         <v>2</v>
       </c>
@@ -3443,7 +3461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="32">
         <v>3</v>
       </c>
@@ -3475,7 +3493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="32">
         <v>4</v>
       </c>
@@ -3507,7 +3525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="32">
         <v>5</v>
       </c>
@@ -3535,7 +3553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="32"/>
       <c r="B9" s="44" t="s">
         <v>200</v>
@@ -3551,7 +3569,7 @@
       <c r="I9" s="41"/>
       <c r="J9" s="41"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="32">
         <v>6</v>
       </c>
@@ -3579,7 +3597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="32">
         <v>7</v>
       </c>
@@ -3611,7 +3629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="32">
         <v>8</v>
       </c>
@@ -3643,7 +3661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="32">
         <v>9</v>
       </c>
@@ -3673,7 +3691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="32">
         <v>10</v>
       </c>
@@ -3701,7 +3719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="32">
         <v>11</v>
       </c>
@@ -3733,7 +3751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="32">
         <v>12</v>
       </c>
@@ -3761,7 +3779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="32">
         <v>13</v>
       </c>
@@ -3789,7 +3807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="32"/>
       <c r="B18" s="32" t="s">
         <v>224</v>
@@ -3805,7 +3823,7 @@
       <c r="I18" s="41"/>
       <c r="J18" s="41"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="32"/>
       <c r="B19" s="32"/>
       <c r="G19" s="32"/>
@@ -3813,7 +3831,7 @@
       <c r="I19" s="41"/>
       <c r="J19" s="41"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="32">
         <v>14</v>
       </c>
@@ -3834,7 +3852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="32">
         <v>15</v>
       </c>
@@ -3855,7 +3873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="32">
         <v>16</v>
       </c>
@@ -3876,7 +3894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="32">
         <v>17</v>
       </c>
@@ -3899,7 +3917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="32">
         <v>18</v>
       </c>
@@ -3920,7 +3938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="32">
         <v>19</v>
       </c>
@@ -3941,7 +3959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="32">
         <v>20</v>
       </c>
@@ -3962,7 +3980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="32">
         <v>21</v>
       </c>
@@ -3983,7 +4001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="32">
         <v>22</v>
       </c>
@@ -4004,7 +4022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="32">
         <v>23</v>
       </c>
@@ -4025,7 +4043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="32">
         <v>24</v>
       </c>
@@ -4046,7 +4064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="32">
         <v>25</v>
       </c>

--- a/Data-file.xlsx
+++ b/Data-file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="749" documentId="8_{3CAE69A3-AE5B-4257-93BE-F3BFAEF5261B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B238CA84-64DD-4AF1-97BF-56752043C7E3}"/>
+  <xr:revisionPtr revIDLastSave="757" documentId="8_{3CAE69A3-AE5B-4257-93BE-F3BFAEF5261B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6498110A-1281-428A-9FBC-7E074D16CFC8}"/>
   <bookViews>
-    <workbookView xWindow="7980" yWindow="4185" windowWidth="18045" windowHeight="11295" xr2:uid="{8A8E2015-1165-48D9-8246-BE8999149D44}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{8A8E2015-1165-48D9-8246-BE8999149D44}"/>
   </bookViews>
   <sheets>
     <sheet name="ACC 3" sheetId="1" r:id="rId1"/>
@@ -105,19 +105,10 @@
     <t>TG Box up</t>
   </si>
   <si>
-    <t>31.08.26/30.09.26/31.10.26</t>
-  </si>
-  <si>
     <t>TG Oil Flushing completion</t>
   </si>
   <si>
-    <t>31.10.26/25.11.26/10.12.27</t>
-  </si>
-  <si>
     <t>Boiler Light up</t>
-  </si>
-  <si>
-    <t>25.10.26/05.12.26/25.12.27</t>
   </si>
   <si>
     <t xml:space="preserve">Steam Blowing Completion </t>
@@ -212,9 +203,6 @@
     <t>In Progress</t>
   </si>
   <si>
-    <t xml:space="preserve"> 30.08.26/30.09.26/15.10.26/30.10.26</t>
-  </si>
-  <si>
     <t>PA 3A</t>
   </si>
   <si>
@@ -650,9 +638,6 @@
     <t>4825 KW</t>
   </si>
   <si>
-    <t>30.09.26/10.10.26/30.10.26</t>
-  </si>
-  <si>
     <t>CEP</t>
   </si>
   <si>
@@ -797,9 +782,6 @@
     <t>11 nos</t>
   </si>
   <si>
-    <t>31.10.26 (Readiness for trial)</t>
-  </si>
-  <si>
     <t>30.09.26/10.10.26/25.10.26/31.10.26</t>
   </si>
   <si>
@@ -807,6 +789,24 @@
   </si>
   <si>
     <t>M&amp;S - Piping works</t>
+  </si>
+  <si>
+    <t>10.11.26 (Readiness for trial)</t>
+  </si>
+  <si>
+    <t>30.09.26/10.10.26/30.10.26/10.11.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 30.08.26/30.09.26/15.10.26/30.10.26/05.11.26</t>
+  </si>
+  <si>
+    <t>31.08.26/30.09.26/31.10.26/15.11.26</t>
+  </si>
+  <si>
+    <t>31.10.26/25.11.26/10.12.27/24.12.26</t>
+  </si>
+  <si>
+    <t>25.10.26/05.12.26/25.12.26</t>
   </si>
 </sst>
 </file>
@@ -1795,10 +1795,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2247,11 +2243,11 @@
         <v>297</v>
       </c>
       <c r="C9" s="30">
-        <v>994</v>
+        <v>1018</v>
       </c>
       <c r="D9" s="31">
         <f>D8+C9</f>
-        <v>5609</v>
+        <v>5633</v>
       </c>
     </row>
   </sheetData>
@@ -2298,55 +2294,55 @@
         <v>18</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>19</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>21</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>23</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -2366,109 +2362,109 @@
   <sheetData>
     <row r="1" spans="1:3" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="23" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="28" t="s">
-        <v>50</v>
-      </c>
       <c r="C7" s="28" t="s">
-        <v>51</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C10" s="29"/>
     </row>
@@ -2487,18 +2483,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B2">
         <v>1448.3</v>
@@ -2509,7 +2505,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B3">
         <v>573.82000000000005</v>
@@ -2536,21 +2532,21 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B2" s="11">
         <v>1200</v>
@@ -2565,7 +2561,7 @@
     </row>
     <row r="3" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B3" s="11">
         <v>300</v>
@@ -2580,7 +2576,7 @@
     </row>
     <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B4" s="11">
         <v>200</v>
@@ -2595,7 +2591,7 @@
     </row>
     <row r="5" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B5" s="12">
         <v>400</v>
@@ -2610,7 +2606,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B6" s="12">
         <v>400</v>
@@ -2625,7 +2621,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B7" s="12">
         <v>250</v>
@@ -2640,7 +2636,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B8" s="12">
         <v>100</v>
@@ -2655,7 +2651,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B9" s="12">
         <v>100</v>
@@ -2670,7 +2666,7 @@
     </row>
     <row r="10" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B10" s="12">
         <f>SUM(B2:B9)</f>
@@ -2718,607 +2714,607 @@
   <sheetData>
     <row r="1" spans="1:12" s="39" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="37" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="F1" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="G1" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="H1" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="I1" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="F1" s="37" t="s">
+      <c r="J1" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="G1" s="37" t="s">
+      <c r="K1" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="H1" s="37" t="s">
+      <c r="L1" s="39" t="s">
         <v>81</v>
-      </c>
-      <c r="I1" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="J1" s="39" t="s">
-        <v>83</v>
-      </c>
-      <c r="K1" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="L1" s="39" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="35" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="F2" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="G2" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="D2" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="E2" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="F2" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="G2" s="35" t="s">
-        <v>92</v>
-      </c>
       <c r="H2" s="35" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="G3" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="H3" s="35" t="s">
         <v>94</v>
-      </c>
-      <c r="C3" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="E3" s="35" t="s">
-        <v>96</v>
-      </c>
-      <c r="F3" s="35" t="s">
-        <v>96</v>
-      </c>
-      <c r="G3" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="H3" s="35" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B4" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" s="35" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4" s="35" t="s">
+        <v>98</v>
+      </c>
+      <c r="G4" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="H4" s="35" t="s">
         <v>99</v>
-      </c>
-      <c r="C4" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="D4" s="35" t="s">
-        <v>101</v>
-      </c>
-      <c r="E4" s="35" t="s">
-        <v>102</v>
-      </c>
-      <c r="F4" s="35" t="s">
-        <v>102</v>
-      </c>
-      <c r="G4" s="35" t="s">
-        <v>92</v>
-      </c>
-      <c r="H4" s="35" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="F5" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="G5" s="35" t="s">
+        <v>85</v>
+      </c>
+      <c r="H5" s="35" t="s">
         <v>106</v>
-      </c>
-      <c r="D5" s="35" t="s">
-        <v>107</v>
-      </c>
-      <c r="E5" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="F5" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="G5" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="H5" s="35" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="E6" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="F6" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="G6" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="C6" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="D6" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="E6" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="F6" s="35" t="s">
-        <v>86</v>
-      </c>
-      <c r="G6" s="35" t="s">
-        <v>116</v>
-      </c>
       <c r="H6" s="35" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H7" s="35" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="35" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G8" s="35" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H8" s="35" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="35" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B9" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="F9" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="G9" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="H9" s="35" t="s">
         <v>125</v>
-      </c>
-      <c r="C9" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="D9" s="35" t="s">
-        <v>127</v>
-      </c>
-      <c r="E9" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="F9" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="G9" s="35" t="s">
-        <v>98</v>
-      </c>
-      <c r="H9" s="35" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="35" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G10" s="35" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="35" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D11" s="38" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E11" s="38" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="G11" s="38" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H11" s="38" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="35" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B12" s="35" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H12" s="38" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="35" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B13" s="35" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D13" s="38" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E13" s="38" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F13" s="38" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G13" s="38" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H13" s="38" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="35" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B14" s="35" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D14" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="E14" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="F14" s="35" t="s">
         <v>116</v>
       </c>
-      <c r="E14" s="35" t="s">
-        <v>92</v>
-      </c>
-      <c r="F14" s="35" t="s">
-        <v>120</v>
-      </c>
       <c r="G14" s="35" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H14" s="35" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="D15" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="E15" s="35" t="s">
         <v>92</v>
       </c>
-      <c r="B15" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="C15" s="35" t="s">
-        <v>144</v>
-      </c>
-      <c r="D15" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="E15" s="35" t="s">
-        <v>96</v>
-      </c>
       <c r="F15" s="35" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G15" s="35" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H15" s="35" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="35" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B16" s="35" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G16" s="38" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H16" s="38" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="35" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B17" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="C17" s="38" t="s">
+        <v>146</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>147</v>
+      </c>
+      <c r="E17" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="F17" s="38" t="s">
         <v>149</v>
       </c>
-      <c r="C17" s="38" t="s">
+      <c r="G17" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="H17" s="38" t="s">
         <v>150</v>
-      </c>
-      <c r="D17" s="38" t="s">
-        <v>151</v>
-      </c>
-      <c r="E17" s="38" t="s">
-        <v>152</v>
-      </c>
-      <c r="F17" s="38" t="s">
-        <v>153</v>
-      </c>
-      <c r="G17" s="38" t="s">
-        <v>119</v>
-      </c>
-      <c r="H17" s="38" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="35" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B18" s="35" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D18" s="35" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E18" s="35" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F18" s="35" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G18" s="35" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H18" s="35" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A19" s="35" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B19" s="35" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D19" s="35" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F19" s="35" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G19" s="35" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H19" s="35" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="35" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B20" s="35" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D20" s="35" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E20" s="35" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F20" s="35" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G20" s="35" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H20" s="35" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="35" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B21" s="35" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D21" s="35" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E21" s="35" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F21" s="35" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G21" s="35" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H21" s="35" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="36"/>
       <c r="B22" s="36"/>
       <c r="C22" s="37" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D22" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="F22" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="G22" s="37" t="s">
+        <v>165</v>
+      </c>
+      <c r="H22" s="37" t="s">
         <v>166</v>
-      </c>
-      <c r="E22" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="F22" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="G22" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="H22" s="37" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="33"/>
       <c r="B23" s="33"/>
       <c r="C23" s="34" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D23" s="33"/>
       <c r="E23" s="34" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F23" s="34" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G23" s="34" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H23" s="34" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="303" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W303" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -3331,6 +3327,7 @@
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.85546875" customWidth="1"/>
     <col min="4" max="4" width="17.5703125" bestFit="1" customWidth="1"/>
@@ -3343,34 +3340,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="42" t="s">
+        <v>173</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>174</v>
+      </c>
+      <c r="C1" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="E1" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="F1" s="42" t="s">
         <v>178</v>
       </c>
-      <c r="C1" s="42" t="s">
+      <c r="G1" s="42" t="s">
         <v>179</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="H1" s="42" t="s">
         <v>180</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="I1" s="42" t="s">
         <v>181</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="J1" s="42" t="s">
         <v>182</v>
-      </c>
-      <c r="G1" s="42" t="s">
-        <v>183</v>
-      </c>
-      <c r="H1" s="42" t="s">
-        <v>184</v>
-      </c>
-      <c r="I1" s="42" t="s">
-        <v>185</v>
-      </c>
-      <c r="J1" s="42" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -3402,22 +3399,22 @@
         <v>1</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C4" s="32">
         <v>1</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E4" s="32">
         <v>11</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H4" s="41">
         <v>1</v>
@@ -3434,22 +3431,22 @@
         <v>2</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C5" s="32">
         <v>2</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E5" s="32">
         <v>11</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="G5" s="32" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="H5" s="41">
         <v>2</v>
@@ -3466,22 +3463,22 @@
         <v>3</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C6" s="32">
         <v>2</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E6" s="32">
         <v>11</v>
       </c>
       <c r="F6" s="32" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="H6" s="41">
         <v>1</v>
@@ -3498,22 +3495,22 @@
         <v>4</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C7" s="32">
         <v>2</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E7" s="32">
         <v>11</v>
       </c>
       <c r="F7" s="32" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="G7" s="32" t="s">
-        <v>197</v>
+        <v>245</v>
       </c>
       <c r="H7" s="41">
         <v>2</v>
@@ -3530,13 +3527,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C8" s="32">
         <v>3</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="E8" s="32">
         <v>11</v>
@@ -3556,13 +3553,13 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="32"/>
       <c r="B9" s="44" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C9" s="45"/>
       <c r="D9" s="45"/>
       <c r="E9" s="46"/>
       <c r="F9" s="32" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="G9" s="32"/>
       <c r="H9" s="41"/>
@@ -3574,13 +3571,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C10" s="32">
         <v>9</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E10" s="32">
         <v>3.3</v>
@@ -3602,22 +3599,22 @@
         <v>7</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C11" s="32">
         <v>1</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E11" s="32">
         <v>3.3</v>
       </c>
       <c r="F11" s="32" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="G11" s="32" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="H11" s="41">
         <v>1</v>
@@ -3634,22 +3631,22 @@
         <v>8</v>
       </c>
       <c r="B12" s="32" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C12" s="32">
         <v>3</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E12" s="32">
         <v>3.3</v>
       </c>
       <c r="F12" s="32" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="G12" s="32" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="H12" s="41">
         <v>3</v>
@@ -3666,19 +3663,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C13" s="32">
         <v>3</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="E13" s="32">
         <v>3.3</v>
       </c>
       <c r="F13" s="32" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="G13" s="32"/>
       <c r="H13" s="41">
@@ -3696,13 +3693,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C14" s="32">
         <v>2</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="E14" s="32">
         <v>3.3</v>
@@ -3724,22 +3721,22 @@
         <v>11</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C15" s="32">
         <v>2</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E15" s="32">
         <v>3.3</v>
       </c>
       <c r="F15" s="32" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="G15" s="32" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="H15" s="41">
         <v>2</v>
@@ -3756,13 +3753,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C16" s="32">
         <v>2</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E16" s="32">
         <v>3.3</v>
@@ -3784,13 +3781,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="32" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C17" s="32">
         <v>2</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="E17" s="32">
         <v>3.3</v>
@@ -3810,13 +3807,13 @@
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="32"/>
       <c r="B18" s="32" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C18" s="32"/>
       <c r="D18" s="32"/>
       <c r="E18" s="32"/>
       <c r="F18" s="32" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G18" s="32"/>
       <c r="H18" s="41"/>
@@ -3836,10 +3833,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="32" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C20" s="32" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="G20" s="32"/>
       <c r="H20" s="41">
@@ -3857,10 +3854,10 @@
         <v>15</v>
       </c>
       <c r="B21" s="32" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C21" s="32" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="G21" s="32"/>
       <c r="H21" s="41">
@@ -3878,10 +3875,10 @@
         <v>16</v>
       </c>
       <c r="B22" s="32" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C22" s="32" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="G22" s="32"/>
       <c r="H22" s="41">
@@ -3899,13 +3896,13 @@
         <v>17</v>
       </c>
       <c r="B23" s="32" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="G23" s="32" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="H23" s="41">
         <v>1</v>
@@ -3922,10 +3919,10 @@
         <v>18</v>
       </c>
       <c r="B24" s="32" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C24" s="32" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="G24" s="32"/>
       <c r="H24" s="41">
@@ -3943,10 +3940,10 @@
         <v>19</v>
       </c>
       <c r="B25" s="32" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C25" s="32" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32">
@@ -3964,10 +3961,10 @@
         <v>20</v>
       </c>
       <c r="B26" s="32" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C26" s="32" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32">
@@ -3985,10 +3982,10 @@
         <v>21</v>
       </c>
       <c r="B27" s="32" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C27" s="32" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="G27" s="32"/>
       <c r="H27" s="32">
@@ -4006,10 +4003,10 @@
         <v>22</v>
       </c>
       <c r="B28" s="32" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C28" s="32" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="G28" s="32"/>
       <c r="H28" s="32">
@@ -4027,10 +4024,10 @@
         <v>23</v>
       </c>
       <c r="B29" s="32" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C29" s="32" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="G29" s="32"/>
       <c r="H29" s="32">
@@ -4048,10 +4045,10 @@
         <v>24</v>
       </c>
       <c r="B30" s="40" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C30" s="32" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="G30" s="32"/>
       <c r="H30" s="32">
@@ -4069,10 +4066,10 @@
         <v>25</v>
       </c>
       <c r="B31" s="40" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C31" s="32" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G31" s="32"/>
       <c r="H31" s="32">
@@ -4087,17 +4084,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="I1:I3"/>
     <mergeCell ref="J1:J3"/>
     <mergeCell ref="C1:C3"/>
     <mergeCell ref="H1:H3"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="G1:G3"/>
     <mergeCell ref="F1:F3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="I1:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
